--- a/grouped_data.xlsx
+++ b/grouped_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU57"/>
+  <dimension ref="A1:CX57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -896,30 +896,45 @@
       </c>
       <c r="CP1" s="1" t="inlineStr">
         <is>
+          <t>Pset_Enrichment.Minimale Höhe</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>Pset_Enrichment.Minimale Breite</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>Pset_Enrichment.Minimale Länge</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
           <t>__pivot_-8.2</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>__pivot_-3.78</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>__pivot_0.0</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>__pivot_2.998</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>__pivot_7.939</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>__pivot_11.947</t>
         </is>
@@ -939,17 +954,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1224, 1225, 1226, 1227</t>
+          <t>1219, 1227, 1228, 1229</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1207.0, 1208.0, 1211.0, 1212.0</t>
+          <t>1212.0, 1207.0, 1208.0, 1211.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0emPRSOwnDOOTgYleM3B_A, 2g6H0ojnvDdueYpZ_5Zux8, 1rOBySJhH5b9YWwDU_guK1, 2Ru4iRmYDDDfo5eLHGZ8RE</t>
+          <t>2Ru4iRmYDDDfo5eLHGZ8RE, 0emPRSOwnDOOTgYleM3B_A, 2g6H0ojnvDdueYpZ_5Zux8, 1rOBySJhH5b9YWwDU_guK1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -969,12 +984,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>KOR:340508, KOR:342423, KOR:343102, KOR:343282</t>
+          <t>KOR:343282, KOR:340508, KOR:342423, KOR:343102</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1224, 1225, 1226, 1227</t>
+          <t>1219, 1227, 1228, 1229</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -1003,12 +1018,12 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>UG2, UG1, OG2, OG3</t>
+          <t>OG3, UG2, UG1, OG2</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-8.2, -3.78, 7.939, 11.947</t>
+          <t>11.947, -8.2, -3.78, 7.939</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr"/>
@@ -1120,22 +1135,22 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knzl, 1QH5Axl111J9SJj2E3W4vx, 0b93QOWH141xpbKCpGEr9v, 3ol_0stLL7q8pSNseENpkf</t>
+          <t>3ol_0stLL7q8pSNseENpkf, 3VbCMl1_928hbAKPG5Knzl, 1QH5Axl111J9SJj2E3W4vx, 0b93QOWH141xpbKCpGEr9v</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>4.121, 3.421, 3.579, 2.522</t>
+          <t>2.522, 4.121, 3.421, 3.579</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>20.2968268134622, 26.887076979177, 22.2995095258837, 24.6411125862649</t>
+          <t>24.6411125862649, 20.2968268134622, 26.887076979177, 22.2995095258837</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>44.2981352255, 61.8464681065, 48.8485630875, 34.166333474</t>
+          <t>34.166333474, 44.2981352255, 61.8464681065, 48.8485630875</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
@@ -1147,22 +1162,25 @@
       <c r="CM2" t="inlineStr"/>
       <c r="CN2" t="inlineStr"/>
       <c r="CO2" t="inlineStr"/>
-      <c r="CP2" t="n">
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="n">
         <v>10.7493655</v>
       </c>
-      <c r="CQ2" t="n">
+      <c r="CT2" t="n">
         <v>18.0784765</v>
       </c>
-      <c r="CR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT2" t="n">
+      <c r="CU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW2" t="n">
         <v>13.6486625</v>
       </c>
-      <c r="CU2" t="n">
+      <c r="CX2" t="n">
         <v>13.547317</v>
       </c>
     </row>
@@ -1180,17 +1198,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1215, 1216, 1219, 1220, 1221, 1222</t>
+          <t>1215, 1216, 1217, 1218, 1223, 1224</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1211.0, 1212.0, 1207.0, 1208.0, 1209.0, 1210.0</t>
+          <t>1209.0, 1210.0, 1211.0, 1212.0, 1207.0, 1208.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18j2PWjBz3nhKzSkJrvM7d, 0wtQ7wfjD5FPd24jrI75yq, 13LOp07jD0lfjp1Ds2xiaX, 3BN76u7jD8SONfck_e054E, 1R$FLavrj8G9Rxnz3lVckG, 0CIMZOOqj8GukY8gSKgU97</t>
+          <t>1R$FLavrj8G9Rxnz3lVckG, 0CIMZOOqj8GukY8gSKgU97, 18j2PWjBz3nhKzSkJrvM7d, 0wtQ7wfjD5FPd24jrI75yq, 13LOp07jD0lfjp1Ds2xiaX, 3BN76u7jD8SONfck_e054E</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1210,12 +1228,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>LUF:343164, LUF:343294, LUF:340252, LUF:342420, LUF:342799, LUF:342961</t>
+          <t>LUF:342799, LUF:342961, LUF:343164, LUF:343294, LUF:340252, LUF:342420</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1215, 1216, 1219, 1220, 1221, 1222</t>
+          <t>1215, 1216, 1217, 1218, 1223, 1224</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -1244,12 +1262,12 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>OG2, OG3, UG2, UG1, EG, OG1</t>
+          <t>EG, OG1, OG2, OG3, UG2, UG1</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>7.939, 11.947, -8.2, -3.78, 0.0, 2.998</t>
+          <t>0.0, 2.998, 7.939, 11.947, -8.2, -3.78</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr"/>
@@ -1361,22 +1379,22 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0b93QOWH141xpbKCpGEr8x, 3ol_0stLL7q8pSNseENpkb, 3VbCMl1_928hbAKPG5Knnl, 1QH5Axl111J9SJj2E3W4vu, 3$FY_ljDfBsweJfZwnfjOk, 0b93QOWH141xpbKCpGErNs</t>
+          <t>3$FY_ljDfBsweJfZwnfjOk, 0b93QOWH141xpbKCpGErNs, 0b93QOWH141xpbKCpGEr8x, 3ol_0stLL7q8pSNseENpkb, 3VbCMl1_928hbAKPG5Knnl, 1QH5Axl111J9SJj2E3W4vu</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>4.008, 2.523, 4.42, 3.421, 3.0, 4.941</t>
+          <t>3.0, 4.941, 4.008, 2.523, 4.42, 3.421</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>7.38232192035912, 7.49144557435166, 7.38098313865425, 58.6046173021893</t>
+          <t>58.6046173021893, 7.38232192035912, 7.49144557435166, 7.38098313865425</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>9.274674324, 5.948525037, 10.22805901, 7.911291707, 89.2932525, 11.4336741105</t>
+          <t>89.2932525, 11.4336741105, 9.274674324, 5.948525037, 10.22805901, 7.911291707</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr"/>
@@ -1384,22 +1402,25 @@
       <c r="CM3" t="inlineStr"/>
       <c r="CN3" t="inlineStr"/>
       <c r="CO3" t="inlineStr"/>
-      <c r="CP3" t="n">
-        <v>2.3140405</v>
-      </c>
-      <c r="CQ3" t="n">
-        <v>2.312567</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>29.7644175</v>
-      </c>
+      <c r="CP3" t="inlineStr"/>
+      <c r="CQ3" t="inlineStr"/>
+      <c r="CR3" t="inlineStr"/>
       <c r="CS3" t="n">
         <v>2.3140405</v>
       </c>
       <c r="CT3" t="n">
+        <v>2.312567</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>29.7644175</v>
+      </c>
+      <c r="CV3" t="n">
         <v>2.3140405</v>
       </c>
-      <c r="CU3" t="n">
+      <c r="CW3" t="n">
+        <v>2.3140405</v>
+      </c>
+      <c r="CX3" t="n">
         <v>2.357719</v>
       </c>
     </row>
@@ -1413,11 +1434,11 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>97.874376</v>
+        <v>97.87437599999998</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1217, 1218, 1228</t>
+          <t>1220, 1221, 1222</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1427,7 +1448,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>34G_SBUtD7Bx_aSDXbyBOH, 11GLlly7bCgPkVa3553rnS, 3Q30KcAwrFjgFId43DWY8P</t>
+          <t>3Q30KcAwrFjgFId43DWY8P, 34G_SBUtD7Bx_aSDXbyBOH, 11GLlly7bCgPkVa3553rnS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1447,12 +1468,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>TRH:341685, TRH:342381, TRH:341682</t>
+          <t>TRH:341682, TRH:341685, TRH:342381</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1217, 1218, 1228</t>
+          <t>1220, 1221, 1222</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1598,7 +1619,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knl6, 1QH5Axl111J9SJj2E3W4w1, 3VbCMl1_928hbAKPG5Knl1</t>
+          <t>3VbCMl1_928hbAKPG5Knl1, 3VbCMl1_928hbAKPG5Knl6, 1QH5Axl111J9SJj2E3W4w1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -1608,12 +1629,12 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>30.404276140697, 30.8427134126076, 10.4407453756904</t>
+          <t>10.4407453756904, 30.404276140697, 30.8427134126076</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>132.984760662, 201.1249740115, 28.0766717725</t>
+          <t>28.0766717725, 132.984760662, 201.1249740115</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
@@ -1625,22 +1646,25 @@
       <c r="CM4" t="inlineStr"/>
       <c r="CN4" t="inlineStr"/>
       <c r="CO4" t="inlineStr"/>
-      <c r="CP4" t="n">
+      <c r="CP4" t="inlineStr"/>
+      <c r="CQ4" t="inlineStr"/>
+      <c r="CR4" t="inlineStr"/>
+      <c r="CS4" t="n">
         <v>39.08309449999999</v>
       </c>
-      <c r="CQ4" t="n">
+      <c r="CT4" t="n">
         <v>58.7912815</v>
       </c>
-      <c r="CR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT4" t="n">
-        <v>0</v>
-      </c>
       <c r="CU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1658,7 +1682,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1223, 1232, 1233, 1234</t>
+          <t>1225, 1226, 1234, 1235</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1668,7 +1692,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1830E3dHD5f9qhMIKx9HB6, 14zTAK7eDFxu25AGckILdY, 3_49$ldkHAGOZei44e_8FY, 0jRMZ$SnH9ouX0ZQEwstxo</t>
+          <t>0jRMZ$SnH9ouX0ZQEwstxo, 1830E3dHD5f9qhMIKx9HB6, 14zTAK7eDFxu25AGckILdY, 3_49$ldkHAGOZei44e_8FY</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1688,12 +1712,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>VRF:342790, VRF:342387, VRF:342402, VRF:342787</t>
+          <t>VRF:342787, VRF:342790, VRF:342387, VRF:342402</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1223, 1232, 1233, 1234</t>
+          <t>1225, 1226, 1234, 1235</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1839,7 +1863,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3$FY_ljDfBsweJfZwnfjOd, 1QH5Axl111J9SJj2E3W4wV, 1QH5Axl111J9SJj2E3W4vk, 3$FY_ljDfBsweJfZwnfjOY</t>
+          <t>3$FY_ljDfBsweJfZwnfjOY, 3$FY_ljDfBsweJfZwnfjOd, 1QH5Axl111J9SJj2E3W4wV, 1QH5Axl111J9SJj2E3W4vk</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -1849,12 +1873,12 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>8.5115559995555, 64.0177644592462, 8.2472826954821, 7.99949280466301</t>
+          <t>7.99949280466301, 8.5115559995555, 64.0177644592462, 8.2472826954821</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>12.423591, 172.6924374945, 14.4110052625, 10.3095015</t>
+          <t>10.3095015, 12.423591, 172.6924374945, 14.4110052625</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
@@ -1866,22 +1890,25 @@
       <c r="CM5" t="inlineStr"/>
       <c r="CN5" t="inlineStr"/>
       <c r="CO5" t="inlineStr"/>
-      <c r="CP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ5" t="n">
+      <c r="CP5" t="inlineStr"/>
+      <c r="CQ5" t="inlineStr"/>
+      <c r="CR5" t="inlineStr"/>
+      <c r="CS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT5" t="n">
         <v>54.69261700000001</v>
       </c>
-      <c r="CR5" t="n">
+      <c r="CU5" t="n">
         <v>7.5776975</v>
       </c>
-      <c r="CS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU5" t="n">
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1899,7 +1926,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1934,7 +1961,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -2119,22 +2146,25 @@
         </is>
       </c>
       <c r="CO6" t="inlineStr"/>
-      <c r="CP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR6" t="n">
+      <c r="CP6" t="inlineStr"/>
+      <c r="CQ6" t="inlineStr"/>
+      <c r="CR6" t="inlineStr"/>
+      <c r="CS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU6" t="n">
         <v>396.6236325</v>
       </c>
-      <c r="CS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU6" t="n">
+      <c r="CV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2152,7 +2182,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2187,7 +2217,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -2372,22 +2402,25 @@
         </is>
       </c>
       <c r="CO7" t="inlineStr"/>
-      <c r="CP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR7" t="n">
+      <c r="CP7" t="inlineStr"/>
+      <c r="CQ7" t="inlineStr"/>
+      <c r="CR7" t="inlineStr"/>
+      <c r="CS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
         <v>29.849794</v>
       </c>
-      <c r="CS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU7" t="n">
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2405,7 +2438,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2440,7 +2473,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -2617,22 +2650,25 @@
       <c r="CM8" t="inlineStr"/>
       <c r="CN8" t="inlineStr"/>
       <c r="CO8" t="inlineStr"/>
-      <c r="CP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR8" t="n">
+      <c r="CP8" t="inlineStr"/>
+      <c r="CQ8" t="inlineStr"/>
+      <c r="CR8" t="inlineStr"/>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
         <v>12.9937485</v>
       </c>
-      <c r="CS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU8" t="n">
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2646,21 +2682,21 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>784.1024639999999</v>
+        <v>784.1024640000001</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1235, 1236, 1237, 1240, 1241, 1242, 1243, 1244, 1247, 1248, 1249, 1250</t>
+          <t>1236, 1237, 1238, 1239, 1241, 1242, 1243, 1244, 1245, 1249, 1250, 1251</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1212.0, 1209.0</t>
+          <t>1209.0, 1212.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2VPJztHKzE5eU2jmaJhVnb, 360G1aSpvFCuurfPO7oVVK, 2gK95MKEPE$O83dwER37Qp, 2u0jNhx4PBahQiA_Mn0fAT, 1XvgrEk2L7Sf0_v9d5iT66, 02z0dETOLCdvSjB6spGLDD, 2dWGfk8A5FP9hGnKCxZb2t, 2smUqi2i10zRE_diOVjJhu, 3Dk2HhiCr35RYXuSaVOvs6, 3AGSwy4Cv9YOBE5MpdNLQt, 0E4QXUam15QfaVaTAymHn2, 0WtOOP9cn9MBUnf0AHUQfJ</t>
+          <t>2smUqi2i10zRE_diOVjJhu, 2VPJztHKzE5eU2jmaJhVnb, 360G1aSpvFCuurfPO7oVVK, 2gK95MKEPE$O83dwER37Qp, 0WtOOP9cn9MBUnf0AHUQfJ, 2u0jNhx4PBahQiA_Mn0fAT, 1XvgrEk2L7Sf0_v9d5iT66, 02z0dETOLCdvSjB6spGLDD, 2dWGfk8A5FP9hGnKCxZb2t, 3Dk2HhiCr35RYXuSaVOvs6, 3AGSwy4Cv9YOBE5MpdNLQt, 0E4QXUam15QfaVaTAymHn2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2680,12 +2716,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>BUF:345410, BUF:345413, BUF:345445, BUF:343916, BUF:343928, BUF:343937, BUF:344088, BUF:345808, BUF:343892, BUF:343901, BUF:343907, BUF:343910</t>
+          <t>BUF:345808, BUF:345410, BUF:345413, BUF:345445, BUF:343910, BUF:343916, BUF:343928, BUF:343937, BUF:344088, BUF:343892, BUF:343901, BUF:343907</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1235, 1236, 1237, 1240, 1241, 1242, 1243, 1244, 1247, 1248, 1249, 1250</t>
+          <t>1236, 1237, 1238, 1239, 1241, 1242, 1243, 1244, 1245, 1249, 1250, 1251</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -2714,12 +2750,12 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>OG3, EG</t>
+          <t>EG, OG3</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.947, 0.0</t>
+          <t>0.0, 11.947</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr"/>
@@ -2831,22 +2867,22 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>2VFBkNPLX5hxPkFzLFhskz, 2VFBkNPLX5hxPkFzLFhskw, 2VFBkNPLX5hxPkFzLFhskQ, 3qJ9B5zvT7$hh913fcAFEL, 3qJ9B5zvT7$hh913fcAFE1, 3qJ9B5zvT7$hh913fcAFDu, 3qJ9B5zvT7$hh913fcA8pX, 3EjVH2xK16fxVS2$WCt57y, 3qJ9B5zvT7$hh913fcAFEj, 3qJ9B5zvT7$hh913fcAFEa, 3qJ9B5zvT7$hh913fcAFEQ, 3qJ9B5zvT7$hh913fcAFEV</t>
+          <t>3EjVH2xK16fxVS2$WCt57y, 2VFBkNPLX5hxPkFzLFhskz, 2VFBkNPLX5hxPkFzLFhskw, 2VFBkNPLX5hxPkFzLFhskQ, 3qJ9B5zvT7$hh913fcAFEV, 3qJ9B5zvT7$hh913fcAFEL, 3qJ9B5zvT7$hh913fcAFE1, 3qJ9B5zvT7$hh913fcAFDu, 3qJ9B5zvT7$hh913fcA8pX, 3qJ9B5zvT7$hh913fcAFEj, 3qJ9B5zvT7$hh913fcAFEa, 3qJ9B5zvT7$hh913fcAFEQ</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>1.001, 1.0</t>
+          <t>1.0, 1.001</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>26.6148846931745, 22.6274169979695, 26.6132231953422, 46.5550926093682, 10.2950212176134, 5.40536512706288, 51.1635370017265, 93.1053783306551, 118.876854433513, 36.0606998520392, 12.0248764381316, 18.0302029491287</t>
+          <t>93.1053783306551, 26.6148846931745, 22.6274169979695, 26.6132231953422, 18.0302029491287, 46.5550926093682, 10.2950212176134, 5.40536512706288, 51.1635370017265, 118.876854433513, 36.0606998520392, 12.0248764381316</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>29.448249831, 32.032, 29.4479620435, 136.0412375, 6.29499, 1.4047875, 17.796225, 330.8825295, 162.444519, 25.4851555, 4.922164, 7.9934815</t>
+          <t>330.8825295, 29.448249831, 32.032, 29.4479620435, 7.9934815, 136.0412375, 6.29499, 1.4047875, 17.796225, 162.444519, 25.4851555, 4.922164</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
@@ -2862,15 +2898,9 @@
       <c r="CM9" t="inlineStr"/>
       <c r="CN9" t="inlineStr"/>
       <c r="CO9" t="inlineStr"/>
-      <c r="CP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>693.2650894999999</v>
-      </c>
+      <c r="CP9" t="inlineStr"/>
+      <c r="CQ9" t="inlineStr"/>
+      <c r="CR9" t="inlineStr"/>
       <c r="CS9" t="n">
         <v>0</v>
       </c>
@@ -2878,6 +2908,15 @@
         <v>0</v>
       </c>
       <c r="CU9" t="n">
+        <v>693.2650895</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX9" t="n">
         <v>90.8373745</v>
       </c>
     </row>
@@ -2895,7 +2934,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1251, 1257, 1258</t>
+          <t>1252, 1253, 1259</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2905,7 +2944,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2VPSmwn8f80wlwsZLQwj7f, 3vBeHUwhfB5OcVQruWBfzN, 2MZESDDfb379fB261rIbnR</t>
+          <t>2MZESDDfb379fB261rIbnR, 2VPSmwn8f80wlwsZLQwj7f, 3vBeHUwhfB5OcVQruWBfzN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2930,7 +2969,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1251, 1257, 1258</t>
+          <t>1252, 1253, 1259</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -3086,12 +3125,12 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>61.8374883969868, 228.018781084836, 61.8367587494543</t>
+          <t>61.8367587494543, 61.8374883969868, 228.018781084836</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>126.372891645, 627.669683, 126.3246569585</t>
+          <t>126.3246569585, 126.372891645, 627.669683</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
@@ -3115,22 +3154,25 @@
         </is>
       </c>
       <c r="CO10" t="inlineStr"/>
-      <c r="CP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR10" t="n">
+      <c r="CP10" t="inlineStr"/>
+      <c r="CQ10" t="inlineStr"/>
+      <c r="CR10" t="inlineStr"/>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" t="n">
         <v>627.669683</v>
       </c>
-      <c r="CS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU10" t="n">
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX10" t="n">
         <v>252.4451035</v>
       </c>
     </row>
@@ -3148,7 +3190,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3183,7 +3225,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -3364,22 +3406,25 @@
         </is>
       </c>
       <c r="CO11" t="inlineStr"/>
-      <c r="CP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR11" t="n">
+      <c r="CP11" t="inlineStr"/>
+      <c r="CQ11" t="inlineStr"/>
+      <c r="CR11" t="inlineStr"/>
+      <c r="CS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
         <v>73.566976</v>
       </c>
-      <c r="CS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU11" t="n">
+      <c r="CV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3397,7 +3442,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3432,7 +3477,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -3613,22 +3658,25 @@
         </is>
       </c>
       <c r="CO12" t="inlineStr"/>
-      <c r="CP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR12" t="n">
+      <c r="CP12" t="inlineStr"/>
+      <c r="CQ12" t="inlineStr"/>
+      <c r="CR12" t="inlineStr"/>
+      <c r="CS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU12" t="n">
         <v>295.86007</v>
       </c>
-      <c r="CS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU12" t="n">
+      <c r="CV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3646,7 +3694,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3681,7 +3729,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -3866,22 +3914,25 @@
         </is>
       </c>
       <c r="CO13" t="inlineStr"/>
-      <c r="CP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR13" t="n">
+      <c r="CP13" t="inlineStr"/>
+      <c r="CQ13" t="inlineStr"/>
+      <c r="CR13" t="inlineStr"/>
+      <c r="CS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU13" t="n">
         <v>17.289957</v>
       </c>
-      <c r="CS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU13" t="n">
+      <c r="CV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3899,7 +3950,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1229, 1230, 1231, 1238, 1239</t>
+          <t>1230, 1231, 1232, 1233, 1240</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3909,7 +3960,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2vZ$D3URf34vJnBMMHx9xX, 1D6v$lAcHDiAsIdGYCYrg4, 14Y66SGP5Fm8iYaOLsp2V8, 0XbzWrb4P70RH_r69FZvNC, 3vSADXkCf9CehgpLlu0Bds</t>
+          <t>3vSADXkCf9CehgpLlu0Bds, 2vZ$D3URf34vJnBMMHx9xX, 1D6v$lAcHDiAsIdGYCYrg4, 14Y66SGP5Fm8iYaOLsp2V8, 0XbzWrb4P70RH_r69FZvNC</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3929,12 +3980,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>UUF:343919, UUF:344049, UUF:344052, UUF:343895, UUF:343913</t>
+          <t>UUF:343913, UUF:343919, UUF:344049, UUF:344052, UUF:343895</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1229, 1230, 1231, 1238, 1239</t>
+          <t>1230, 1231, 1232, 1233, 1240</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -4080,7 +4131,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEM, 3qJ9B5zvT7$hh913fcAFC8, 3qJ9B5zvT7$hh913fcAFCD, 3qJ9B5zvT7$hh913fcAFEk, 3qJ9B5zvT7$hh913fcAFEG</t>
+          <t>3qJ9B5zvT7$hh913fcAFEG, 3qJ9B5zvT7$hh913fcAFEM, 3qJ9B5zvT7$hh913fcAFC8, 3qJ9B5zvT7$hh913fcAFCD, 3qJ9B5zvT7$hh913fcAFEk</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -4090,12 +4141,12 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>27.1971243796257, 165.175783539062, 32.1979140750708, 71.8572432719856, 28.3650362774305</t>
+          <t>28.3650362774305, 27.1971243796257, 165.175783539062, 32.1979140750708, 71.8572432719856</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t>35.7954435, 258.794827, 56.537983, 24.9312215, 13.032036</t>
+          <t>13.032036, 35.7954435, 258.794827, 56.537983, 24.9312215</t>
         </is>
       </c>
       <c r="CK14" t="inlineStr">
@@ -4111,22 +4162,25 @@
       <c r="CM14" t="inlineStr"/>
       <c r="CN14" t="inlineStr"/>
       <c r="CO14" t="inlineStr"/>
-      <c r="CP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR14" t="n">
+      <c r="CP14" t="inlineStr"/>
+      <c r="CQ14" t="inlineStr"/>
+      <c r="CR14" t="inlineStr"/>
+      <c r="CS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU14" t="n">
         <v>389.091511</v>
       </c>
-      <c r="CS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU14" t="n">
+      <c r="CV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4144,7 +4198,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4179,7 +4233,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -4360,22 +4414,25 @@
       </c>
       <c r="CN15" t="inlineStr"/>
       <c r="CO15" t="inlineStr"/>
-      <c r="CP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR15" t="n">
+      <c r="CP15" t="inlineStr"/>
+      <c r="CQ15" t="inlineStr"/>
+      <c r="CR15" t="inlineStr"/>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
         <v>5.20168</v>
       </c>
-      <c r="CS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU15" t="n">
+      <c r="CV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4393,7 +4450,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4428,7 +4485,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -4609,22 +4666,25 @@
       </c>
       <c r="CN16" t="inlineStr"/>
       <c r="CO16" t="inlineStr"/>
-      <c r="CP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR16" t="n">
+      <c r="CP16" t="inlineStr"/>
+      <c r="CQ16" t="inlineStr"/>
+      <c r="CR16" t="inlineStr"/>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU16" t="n">
         <v>18.206341</v>
       </c>
-      <c r="CS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU16" t="n">
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4858,22 +4918,25 @@
         </is>
       </c>
       <c r="CO17" t="inlineStr"/>
-      <c r="CP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR17" t="n">
+      <c r="CP17" t="inlineStr"/>
+      <c r="CQ17" t="inlineStr"/>
+      <c r="CR17" t="inlineStr"/>
+      <c r="CS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU17" t="n">
         <v>71.548801</v>
       </c>
-      <c r="CS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU17" t="n">
+      <c r="CV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5103,22 +5166,25 @@
         </is>
       </c>
       <c r="CO18" t="inlineStr"/>
-      <c r="CP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR18" t="n">
+      <c r="CP18" t="inlineStr"/>
+      <c r="CQ18" t="inlineStr"/>
+      <c r="CR18" t="inlineStr"/>
+      <c r="CS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU18" t="n">
         <v>53.9113785</v>
       </c>
-      <c r="CS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU18" t="n">
+      <c r="CV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5348,22 +5414,25 @@
         </is>
       </c>
       <c r="CO19" t="inlineStr"/>
-      <c r="CP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>0</v>
-      </c>
+      <c r="CP19" t="inlineStr"/>
+      <c r="CQ19" t="inlineStr"/>
+      <c r="CR19" t="inlineStr"/>
       <c r="CS19" t="n">
         <v>0</v>
       </c>
       <c r="CT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW19" t="n">
         <v>17.5731125</v>
       </c>
-      <c r="CU19" t="n">
+      <c r="CX19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5597,22 +5666,25 @@
         </is>
       </c>
       <c r="CO20" t="inlineStr"/>
-      <c r="CP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR20" t="n">
+      <c r="CP20" t="inlineStr"/>
+      <c r="CQ20" t="inlineStr"/>
+      <c r="CR20" t="inlineStr"/>
+      <c r="CS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU20" t="n">
         <v>64.21340600000001</v>
       </c>
-      <c r="CS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU20" t="n">
+      <c r="CV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5842,22 +5914,25 @@
         </is>
       </c>
       <c r="CO21" t="inlineStr"/>
-      <c r="CP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR21" t="n">
+      <c r="CP21" t="inlineStr"/>
+      <c r="CQ21" t="inlineStr"/>
+      <c r="CR21" t="inlineStr"/>
+      <c r="CS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU21" t="n">
         <v>6.9409425</v>
       </c>
-      <c r="CS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU21" t="n">
+      <c r="CV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6091,22 +6166,25 @@
         </is>
       </c>
       <c r="CO22" t="inlineStr"/>
-      <c r="CP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR22" t="n">
+      <c r="CP22" t="inlineStr"/>
+      <c r="CQ22" t="inlineStr"/>
+      <c r="CR22" t="inlineStr"/>
+      <c r="CS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU22" t="n">
         <v>4.44016</v>
       </c>
-      <c r="CS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU22" t="n">
+      <c r="CV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6336,22 +6414,25 @@
         </is>
       </c>
       <c r="CO23" t="inlineStr"/>
-      <c r="CP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR23" t="n">
+      <c r="CP23" t="inlineStr"/>
+      <c r="CQ23" t="inlineStr"/>
+      <c r="CR23" t="inlineStr"/>
+      <c r="CS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU23" t="n">
         <v>7.189814</v>
       </c>
-      <c r="CS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU23" t="n">
+      <c r="CV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6589,22 +6670,25 @@
           <t>3.0</t>
         </is>
       </c>
-      <c r="CP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR24" t="n">
+      <c r="CP24" t="inlineStr"/>
+      <c r="CQ24" t="inlineStr"/>
+      <c r="CR24" t="inlineStr"/>
+      <c r="CS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU24" t="n">
         <v>72.32068099999999</v>
       </c>
-      <c r="CS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU24" t="n">
+      <c r="CV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6834,22 +6918,25 @@
         </is>
       </c>
       <c r="CO25" t="inlineStr"/>
-      <c r="CP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR25" t="n">
+      <c r="CP25" t="inlineStr"/>
+      <c r="CQ25" t="inlineStr"/>
+      <c r="CR25" t="inlineStr"/>
+      <c r="CS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU25" t="n">
         <v>123.877062</v>
       </c>
-      <c r="CS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU25" t="n">
+      <c r="CV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7083,22 +7170,25 @@
         </is>
       </c>
       <c r="CO26" t="inlineStr"/>
-      <c r="CP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ26" t="n">
+      <c r="CP26" t="inlineStr"/>
+      <c r="CQ26" t="inlineStr"/>
+      <c r="CR26" t="inlineStr"/>
+      <c r="CS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT26" t="n">
         <v>2.8944635</v>
       </c>
-      <c r="CR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT26" t="n">
-        <v>0</v>
-      </c>
       <c r="CU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7332,22 +7422,25 @@
         </is>
       </c>
       <c r="CO27" t="inlineStr"/>
-      <c r="CP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ27" t="n">
+      <c r="CP27" t="inlineStr"/>
+      <c r="CQ27" t="inlineStr"/>
+      <c r="CR27" t="inlineStr"/>
+      <c r="CS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT27" t="n">
         <v>2.719245</v>
       </c>
-      <c r="CR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT27" t="n">
-        <v>0</v>
-      </c>
       <c r="CU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7365,7 +7458,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -7400,7 +7493,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -7585,22 +7678,25 @@
           <t>3.5</t>
         </is>
       </c>
-      <c r="CP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ28" t="n">
+      <c r="CP28" t="inlineStr"/>
+      <c r="CQ28" t="inlineStr"/>
+      <c r="CR28" t="inlineStr"/>
+      <c r="CS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT28" t="n">
         <v>25.280915</v>
       </c>
-      <c r="CR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT28" t="n">
-        <v>0</v>
-      </c>
       <c r="CU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7618,7 +7714,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1264, 1265</t>
+          <t>1265, 1266</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -7653,7 +7749,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1264, 1265</t>
+          <t>1265, 1266</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -7838,22 +7934,25 @@
           <t>3.5</t>
         </is>
       </c>
-      <c r="CP29" t="n">
+      <c r="CP29" t="inlineStr"/>
+      <c r="CQ29" t="inlineStr"/>
+      <c r="CR29" t="inlineStr"/>
+      <c r="CS29" t="n">
         <v>68.07347249999999</v>
       </c>
-      <c r="CQ29" t="n">
+      <c r="CT29" t="n">
         <v>13.790366</v>
       </c>
-      <c r="CR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT29" t="n">
-        <v>0</v>
-      </c>
       <c r="CU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7871,7 +7970,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -7906,7 +8005,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -8091,22 +8190,25 @@
           <t>3.5</t>
         </is>
       </c>
-      <c r="CP30" t="n">
+      <c r="CP30" t="inlineStr"/>
+      <c r="CQ30" t="inlineStr"/>
+      <c r="CR30" t="inlineStr"/>
+      <c r="CS30" t="n">
         <v>130.4597315</v>
       </c>
-      <c r="CQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS30" t="n">
-        <v>0</v>
-      </c>
       <c r="CT30" t="n">
         <v>0</v>
       </c>
       <c r="CU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8124,7 +8226,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -8159,7 +8261,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -8344,22 +8446,25 @@
           <t>3.5</t>
         </is>
       </c>
-      <c r="CP31" t="n">
+      <c r="CP31" t="inlineStr"/>
+      <c r="CQ31" t="inlineStr"/>
+      <c r="CR31" t="inlineStr"/>
+      <c r="CS31" t="n">
         <v>38.861445</v>
       </c>
-      <c r="CQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS31" t="n">
-        <v>0</v>
-      </c>
       <c r="CT31" t="n">
         <v>0</v>
       </c>
       <c r="CU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8541,22 +8646,25 @@
       <c r="CM32" t="inlineStr"/>
       <c r="CN32" t="inlineStr"/>
       <c r="CO32" t="inlineStr"/>
-      <c r="CP32" t="n">
+      <c r="CP32" t="inlineStr"/>
+      <c r="CQ32" t="inlineStr"/>
+      <c r="CR32" t="inlineStr"/>
+      <c r="CS32" t="n">
         <v>946.7568455000001</v>
       </c>
-      <c r="CQ32" t="n">
+      <c r="CT32" t="n">
         <v>944.3010395</v>
       </c>
-      <c r="CR32" t="n">
+      <c r="CU32" t="n">
         <v>635.4141235</v>
       </c>
-      <c r="CS32" t="n">
+      <c r="CV32" t="n">
         <v>607.3553475</v>
       </c>
-      <c r="CT32" t="n">
+      <c r="CW32" t="n">
         <v>607.3728175</v>
       </c>
-      <c r="CU32" t="n">
+      <c r="CX32" t="n">
         <v>144.2348565</v>
       </c>
     </row>
@@ -8738,22 +8846,25 @@
       <c r="CM33" t="inlineStr"/>
       <c r="CN33" t="inlineStr"/>
       <c r="CO33" t="inlineStr"/>
-      <c r="CP33" t="n">
+      <c r="CP33" t="inlineStr"/>
+      <c r="CQ33" t="inlineStr"/>
+      <c r="CR33" t="inlineStr"/>
+      <c r="CS33" t="n">
         <v>1893.5052305</v>
       </c>
-      <c r="CQ33" t="n">
+      <c r="CT33" t="n">
         <v>944.3010395</v>
       </c>
-      <c r="CR33" t="n">
+      <c r="CU33" t="n">
         <v>1280.054072</v>
       </c>
-      <c r="CS33" t="n">
+      <c r="CV33" t="n">
         <v>615.1939470000001</v>
       </c>
-      <c r="CT33" t="n">
+      <c r="CW33" t="n">
         <v>607.3728175</v>
       </c>
-      <c r="CU33" t="n">
+      <c r="CX33" t="n">
         <v>144.2348565</v>
       </c>
     </row>
@@ -8987,22 +9098,25 @@
         </is>
       </c>
       <c r="CO34" t="inlineStr"/>
-      <c r="CP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR34" t="n">
+      <c r="CP34" t="inlineStr"/>
+      <c r="CQ34" t="inlineStr"/>
+      <c r="CR34" t="inlineStr"/>
+      <c r="CS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU34" t="n">
         <v>11.070615</v>
       </c>
-      <c r="CS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU34" t="n">
+      <c r="CV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9236,22 +9350,25 @@
         </is>
       </c>
       <c r="CO35" t="inlineStr"/>
-      <c r="CP35" t="n">
+      <c r="CP35" t="inlineStr"/>
+      <c r="CQ35" t="inlineStr"/>
+      <c r="CR35" t="inlineStr"/>
+      <c r="CS35" t="n">
         <v>11.5049595</v>
       </c>
-      <c r="CQ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS35" t="n">
-        <v>0</v>
-      </c>
       <c r="CT35" t="n">
         <v>0</v>
       </c>
       <c r="CU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9485,22 +9602,25 @@
         </is>
       </c>
       <c r="CO36" t="inlineStr"/>
-      <c r="CP36" t="n">
+      <c r="CP36" t="inlineStr"/>
+      <c r="CQ36" t="inlineStr"/>
+      <c r="CR36" t="inlineStr"/>
+      <c r="CS36" t="n">
         <v>24.194584</v>
       </c>
-      <c r="CQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS36" t="n">
-        <v>0</v>
-      </c>
       <c r="CT36" t="n">
         <v>0</v>
       </c>
       <c r="CU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9734,22 +9854,25 @@
         </is>
       </c>
       <c r="CO37" t="inlineStr"/>
-      <c r="CP37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ37" t="n">
+      <c r="CP37" t="inlineStr"/>
+      <c r="CQ37" t="inlineStr"/>
+      <c r="CR37" t="inlineStr"/>
+      <c r="CS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT37" t="n">
         <v>3.582502</v>
       </c>
-      <c r="CR37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT37" t="n">
+      <c r="CU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW37" t="n">
         <v>4.3787245</v>
       </c>
-      <c r="CU37" t="n">
+      <c r="CX37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9767,7 +9890,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -9802,7 +9925,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -9983,22 +10106,25 @@
         </is>
       </c>
       <c r="CO38" t="inlineStr"/>
-      <c r="CP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR38" t="n">
+      <c r="CP38" t="inlineStr"/>
+      <c r="CQ38" t="inlineStr"/>
+      <c r="CR38" t="inlineStr"/>
+      <c r="CS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU38" t="n">
         <v>14.9977755</v>
       </c>
-      <c r="CS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU38" t="n">
+      <c r="CV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10016,7 +10142,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -10051,7 +10177,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -10228,22 +10354,25 @@
         </is>
       </c>
       <c r="CO39" t="inlineStr"/>
-      <c r="CP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR39" t="n">
+      <c r="CP39" t="inlineStr"/>
+      <c r="CQ39" t="inlineStr"/>
+      <c r="CR39" t="inlineStr"/>
+      <c r="CS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU39" t="n">
         <v>34.123994</v>
       </c>
-      <c r="CS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU39" t="n">
+      <c r="CV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10477,22 +10606,25 @@
         </is>
       </c>
       <c r="CO40" t="inlineStr"/>
-      <c r="CP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ40" t="n">
+      <c r="CP40" t="inlineStr"/>
+      <c r="CQ40" t="inlineStr"/>
+      <c r="CR40" t="inlineStr"/>
+      <c r="CS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT40" t="n">
         <v>31.359346</v>
       </c>
-      <c r="CR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT40" t="n">
-        <v>0</v>
-      </c>
       <c r="CU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10510,7 +10642,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1271, 1273, 1274, 1275</t>
+          <t>1271, 1272, 1275, 1276</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -10520,7 +10652,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2oV52czXD7zAOL8XOUSL78, 1d_UGp1UD2pfCq6QCu1odj, 1DjBk084n8gfRcElXcnhlR, 1vDbowLhr7nx5SdmnF8FXc</t>
+          <t>1vDbowLhr7nx5SdmnF8FXc, 2oV52czXD7zAOL8XOUSL78, 1d_UGp1UD2pfCq6QCu1odj, 1DjBk084n8gfRcElXcnhlR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -10540,12 +10672,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>GSA:342378, GSA:342369, GSA:342372, GSA:342375</t>
+          <t>GSA:342375, GSA:342378, GSA:342369, GSA:342372</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1271, 1273, 1274, 1275</t>
+          <t>1271, 1272, 1275, 1276</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -10691,7 +10823,7 @@
       </c>
       <c r="CG41" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4w6, 1QH5Axl111J9SJj2E3W4wD, 1QH5Axl111J9SJj2E3W4w8, 1QH5Axl111J9SJj2E3W4wB</t>
+          <t>1QH5Axl111J9SJj2E3W4wB, 1QH5Axl111J9SJj2E3W4w6, 1QH5Axl111J9SJj2E3W4wD, 1QH5Axl111J9SJj2E3W4w8</t>
         </is>
       </c>
       <c r="CH41" t="inlineStr">
@@ -10701,12 +10833,12 @@
       </c>
       <c r="CI41" t="inlineStr">
         <is>
-          <t>38.5665051072028, 38.597841235775, 38.5011315279237, 38.5924363426088</t>
+          <t>38.5924363426088, 38.5665051072028, 38.597841235775, 38.5011315279237</t>
         </is>
       </c>
       <c r="CJ41" t="inlineStr">
         <is>
-          <t>143.9881367375, 144.686432968, 143.321228182, 144.861656588</t>
+          <t>144.861656588, 143.9881367375, 144.686432968, 143.321228182</t>
         </is>
       </c>
       <c r="CK41" t="inlineStr">
@@ -10726,22 +10858,25 @@
         </is>
       </c>
       <c r="CO41" t="inlineStr"/>
-      <c r="CP41" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ41" t="n">
+      <c r="CP41" t="inlineStr"/>
+      <c r="CQ41" t="inlineStr"/>
+      <c r="CR41" t="inlineStr"/>
+      <c r="CS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT41" t="n">
         <v>168.6224655</v>
       </c>
-      <c r="CR41" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS41" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT41" t="n">
-        <v>0</v>
-      </c>
       <c r="CU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10759,7 +10894,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -10794,7 +10929,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -10975,22 +11110,25 @@
         </is>
       </c>
       <c r="CO42" t="inlineStr"/>
-      <c r="CP42" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR42" t="n">
+      <c r="CP42" t="inlineStr"/>
+      <c r="CQ42" t="inlineStr"/>
+      <c r="CR42" t="inlineStr"/>
+      <c r="CS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU42" t="n">
         <v>13.396027</v>
       </c>
-      <c r="CS42" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT42" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU42" t="n">
+      <c r="CV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11224,22 +11362,25 @@
         </is>
       </c>
       <c r="CO43" t="inlineStr"/>
-      <c r="CP43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR43" t="n">
-        <v>0</v>
-      </c>
+      <c r="CP43" t="inlineStr"/>
+      <c r="CQ43" t="inlineStr"/>
+      <c r="CR43" t="inlineStr"/>
       <c r="CS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV43" t="n">
         <v>11.810404</v>
       </c>
-      <c r="CT43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU43" t="n">
+      <c r="CW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11257,17 +11398,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1277, 1278</t>
+          <t>1273, 1278</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1207.0, 1210.0</t>
+          <t>1210.0, 1207.0</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1OOeb7pNP5YhVqjcacSVQj, 1FDFHpwUH4NB1tapjSpmKb</t>
+          <t>1FDFHpwUH4NB1tapjSpmKb, 1OOeb7pNP5YhVqjcacSVQj</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -11287,12 +11428,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SGR:340482, SGR:342955</t>
+          <t>SGR:342955, SGR:340482</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1277, 1278</t>
+          <t>1273, 1278</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -11321,12 +11462,12 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>UG2, OG1</t>
+          <t>OG1, UG2</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>-8.2, 2.998</t>
+          <t>2.998, -8.2</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr"/>
@@ -11438,22 +11579,22 @@
       </c>
       <c r="CG44" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knzn, 0b93QOWH141xpbKCpGErNi</t>
+          <t>0b93QOWH141xpbKCpGErNi, 3VbCMl1_928hbAKPG5Knzn</t>
         </is>
       </c>
       <c r="CH44" t="inlineStr">
         <is>
-          <t>4.121, 3.982</t>
+          <t>3.982, 4.121</t>
         </is>
       </c>
       <c r="CI44" t="inlineStr">
         <is>
-          <t>37.9925325891083, 41.7997852969898</t>
+          <t>41.7997852969898, 37.9925325891083</t>
         </is>
       </c>
       <c r="CJ44" t="inlineStr">
         <is>
-          <t>370.300717605, 356.711573856</t>
+          <t>356.711573856, 370.300717605</t>
         </is>
       </c>
       <c r="CK44" t="inlineStr">
@@ -11473,22 +11614,25 @@
         </is>
       </c>
       <c r="CO44" t="inlineStr"/>
-      <c r="CP44" t="n">
+      <c r="CP44" t="inlineStr"/>
+      <c r="CQ44" t="inlineStr"/>
+      <c r="CR44" t="inlineStr"/>
+      <c r="CS44" t="n">
         <v>89.857005</v>
       </c>
-      <c r="CQ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR44" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS44" t="n">
+      <c r="CT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV44" t="n">
         <v>89.581008</v>
       </c>
-      <c r="CT44" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU44" t="n">
+      <c r="CW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11506,7 +11650,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1276, 1282</t>
+          <t>1277, 1282</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -11541,7 +11685,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1276, 1282</t>
+          <t>1277, 1282</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -11726,22 +11870,37 @@
           <t>7.0</t>
         </is>
       </c>
-      <c r="CP45" t="n">
+      <c r="CP45" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="CQ45" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="CR45" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="CS45" t="n">
         <v>463.376039</v>
       </c>
-      <c r="CQ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR45" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS45" t="n">
+      <c r="CT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV45" t="n">
         <v>463.384951</v>
       </c>
-      <c r="CT45" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU45" t="n">
+      <c r="CW45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11975,22 +12134,25 @@
         </is>
       </c>
       <c r="CO46" t="inlineStr"/>
-      <c r="CP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ46" t="n">
+      <c r="CP46" t="inlineStr"/>
+      <c r="CQ46" t="inlineStr"/>
+      <c r="CR46" t="inlineStr"/>
+      <c r="CS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT46" t="n">
         <v>9.246236</v>
       </c>
-      <c r="CR46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS46" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT46" t="n">
+      <c r="CU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW46" t="n">
         <v>6.381486</v>
       </c>
-      <c r="CU46" t="n">
+      <c r="CX46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12224,22 +12386,25 @@
         </is>
       </c>
       <c r="CO47" t="inlineStr"/>
-      <c r="CP47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ47" t="n">
+      <c r="CP47" t="inlineStr"/>
+      <c r="CQ47" t="inlineStr"/>
+      <c r="CR47" t="inlineStr"/>
+      <c r="CS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT47" t="n">
         <v>11.0386675</v>
       </c>
-      <c r="CR47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS47" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT47" t="n">
+      <c r="CU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW47" t="n">
         <v>4.561436</v>
       </c>
-      <c r="CU47" t="n">
+      <c r="CX47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12473,22 +12638,25 @@
         </is>
       </c>
       <c r="CO48" t="inlineStr"/>
-      <c r="CP48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ48" t="n">
+      <c r="CP48" t="inlineStr"/>
+      <c r="CQ48" t="inlineStr"/>
+      <c r="CR48" t="inlineStr"/>
+      <c r="CS48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT48" t="n">
         <v>3.934619</v>
       </c>
-      <c r="CR48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS48" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT48" t="n">
-        <v>0</v>
-      </c>
       <c r="CU48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12718,15 +12886,9 @@
         </is>
       </c>
       <c r="CO49" t="inlineStr"/>
-      <c r="CP49" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR49" t="n">
-        <v>0</v>
-      </c>
+      <c r="CP49" t="inlineStr"/>
+      <c r="CQ49" t="inlineStr"/>
+      <c r="CR49" t="inlineStr"/>
       <c r="CS49" t="n">
         <v>0</v>
       </c>
@@ -12734,6 +12896,15 @@
         <v>0</v>
       </c>
       <c r="CU49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX49" t="n">
         <v>17.564029</v>
       </c>
     </row>
@@ -12967,22 +13138,25 @@
         </is>
       </c>
       <c r="CO50" t="inlineStr"/>
-      <c r="CP50" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR50" t="n">
+      <c r="CP50" t="inlineStr"/>
+      <c r="CQ50" t="inlineStr"/>
+      <c r="CR50" t="inlineStr"/>
+      <c r="CS50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU50" t="n">
         <v>20.323617</v>
       </c>
-      <c r="CS50" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT50" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU50" t="n">
+      <c r="CV50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13216,15 +13390,9 @@
         </is>
       </c>
       <c r="CO51" t="inlineStr"/>
-      <c r="CP51" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR51" t="n">
-        <v>0</v>
-      </c>
+      <c r="CP51" t="inlineStr"/>
+      <c r="CQ51" t="inlineStr"/>
+      <c r="CR51" t="inlineStr"/>
       <c r="CS51" t="n">
         <v>0</v>
       </c>
@@ -13232,6 +13400,15 @@
         <v>0</v>
       </c>
       <c r="CU51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX51" t="n">
         <v>35.5960265</v>
       </c>
     </row>
@@ -13461,15 +13638,9 @@
         </is>
       </c>
       <c r="CO52" t="inlineStr"/>
-      <c r="CP52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR52" t="n">
-        <v>0</v>
-      </c>
+      <c r="CP52" t="inlineStr"/>
+      <c r="CQ52" t="inlineStr"/>
+      <c r="CR52" t="inlineStr"/>
       <c r="CS52" t="n">
         <v>0</v>
       </c>
@@ -13477,6 +13648,15 @@
         <v>0</v>
       </c>
       <c r="CU52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX52" t="n">
         <v>17.564029</v>
       </c>
     </row>
@@ -13706,15 +13886,9 @@
         </is>
       </c>
       <c r="CO53" t="inlineStr"/>
-      <c r="CP53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR53" t="n">
-        <v>0</v>
-      </c>
+      <c r="CP53" t="inlineStr"/>
+      <c r="CQ53" t="inlineStr"/>
+      <c r="CR53" t="inlineStr"/>
       <c r="CS53" t="n">
         <v>0</v>
       </c>
@@ -13722,6 +13896,15 @@
         <v>0</v>
       </c>
       <c r="CU53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX53" t="n">
         <v>35.517629</v>
       </c>
     </row>
@@ -13959,22 +14142,25 @@
           <t>3.0</t>
         </is>
       </c>
-      <c r="CP54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR54" t="n">
+      <c r="CP54" t="inlineStr"/>
+      <c r="CQ54" t="inlineStr"/>
+      <c r="CR54" t="inlineStr"/>
+      <c r="CS54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU54" t="n">
         <v>90.066202</v>
       </c>
-      <c r="CS54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT54" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU54" t="n">
+      <c r="CV54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14204,22 +14390,25 @@
         </is>
       </c>
       <c r="CO55" t="inlineStr"/>
-      <c r="CP55" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR55" t="n">
-        <v>0</v>
-      </c>
+      <c r="CP55" t="inlineStr"/>
+      <c r="CQ55" t="inlineStr"/>
+      <c r="CR55" t="inlineStr"/>
       <c r="CS55" t="n">
         <v>0</v>
       </c>
       <c r="CT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW55" t="n">
         <v>51.768942</v>
       </c>
-      <c r="CU55" t="n">
+      <c r="CX55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14409,22 +14598,25 @@
       <c r="CM56" t="inlineStr"/>
       <c r="CN56" t="inlineStr"/>
       <c r="CO56" t="inlineStr"/>
-      <c r="CP56" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR56" t="n">
+      <c r="CP56" t="inlineStr"/>
+      <c r="CQ56" t="inlineStr"/>
+      <c r="CR56" t="inlineStr"/>
+      <c r="CS56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU56" t="n">
         <v>16.361301</v>
       </c>
-      <c r="CS56" t="n">
+      <c r="CV56" t="n">
         <v>50.5339195</v>
       </c>
-      <c r="CT56" t="n">
+      <c r="CW56" t="n">
         <v>57.0922475</v>
       </c>
-      <c r="CU56" t="n">
+      <c r="CX56" t="n">
         <v>40.6284265</v>
       </c>
     </row>
@@ -14614,22 +14806,25 @@
       <c r="CM57" t="inlineStr"/>
       <c r="CN57" t="inlineStr"/>
       <c r="CO57" t="inlineStr"/>
-      <c r="CP57" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR57" t="n">
+      <c r="CP57" t="inlineStr"/>
+      <c r="CQ57" t="inlineStr"/>
+      <c r="CR57" t="inlineStr"/>
+      <c r="CS57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU57" t="n">
         <v>6.8265125</v>
       </c>
-      <c r="CS57" t="n">
+      <c r="CV57" t="n">
         <v>6.8265125</v>
       </c>
-      <c r="CT57" t="n">
+      <c r="CW57" t="n">
         <v>6.8265125</v>
       </c>
-      <c r="CU57" t="n">
+      <c r="CX57" t="n">
         <v>6.8265125</v>
       </c>
     </row>

--- a/grouped_data.xlsx
+++ b/grouped_data.xlsx
@@ -556,34 +556,34 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>ePset_abstractBIM.PredefinedType</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ePset_abstractBIM.IsExternal</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ePset_abstractBIM.Spaces</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ePset_abstractBIM.SpacesLongName</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ePset_abstractBIM.SpacesName</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
           <t>Pset_CoveringCommon.IsExternal</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>ePset_abstractBIM.PredefinedType</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>ePset_abstractBIM.IsExternal</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>ePset_abstractBIM.Spaces</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>ePset_abstractBIM.SpacesLongName</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>ePset_abstractBIM.SpacesName</t>
-        </is>
-      </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Pset_SpatialData.BuildingStory</t>
@@ -931,12 +931,12 @@
       </c>
       <c r="CW1" s="1" t="inlineStr">
         <is>
-          <t>__pivot_7.939</t>
+          <t>__pivot_7.94</t>
         </is>
       </c>
       <c r="CX1" s="1" t="inlineStr">
         <is>
-          <t>__pivot_11.947</t>
+          <t>__pivot_11.948</t>
         </is>
       </c>
     </row>
@@ -954,17 +954,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1219, 1227, 1228, 1229</t>
+          <t>1202, 1203, 1204, 1205</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1212.0, 1207.0, 1208.0, 1211.0</t>
+          <t>1183.0, 1184.0, 1187.0, 1188.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2Ru4iRmYDDDfo5eLHGZ8RE, 0emPRSOwnDOOTgYleM3B_A, 2g6H0ojnvDdueYpZ_5Zux8, 1rOBySJhH5b9YWwDU_guK1</t>
+          <t>24xm6C08LB6PmPlweCGB8I, 0zR70dM_L5hgHRsQfW3Yo7, 1jaqyoTjT5Bhtkj1U9RyUu, 3yI4yvxYX9aBv$Jk3GB$dy</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -984,12 +984,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>KOR:343282, KOR:340508, KOR:342423, KOR:343102</t>
+          <t>KOR:340508, KOR:342423, KOR:343102, KOR:343282</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1219, 1227, 1228, 1229</t>
+          <t>1202, 1203, 1204, 1205</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -1018,12 +1018,12 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>OG3, UG2, UG1, OG2</t>
+          <t>UG2, UG1, OG2, OG3</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>11.947, -8.2, -3.78, 7.939</t>
+          <t>-8.2, -3.78, 7.94, 11.948</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr"/>
@@ -1135,22 +1135,22 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3ol_0stLL7q8pSNseENpkf, 3VbCMl1_928hbAKPG5Knzl, 1QH5Axl111J9SJj2E3W4vx, 0b93QOWH141xpbKCpGEr9v</t>
+          <t>3VbCMl1_928hbAKPG5Knzl, 1QH5Axl111J9SJj2E3W4vx, 0b93QOWH141xpbKCpGEr9v, 3ol_0stLL7q8pSNseENpkf</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>2.522, 4.121, 3.421, 3.579</t>
+          <t>4.12, 3.42000304025274, 3.57800180084113, 2.522</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>24.6411125862649, 20.2968268134622, 26.887076979177, 22.2995095258837</t>
+          <t>20.2968268134622, 26.887076979177, 22.2995095258837, 24.6411125862649</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>34.166333474, 44.2981352255, 61.8464681065, 48.8485630875</t>
+          <t>44.28738586, 61.8284445931377, 48.8349390040728, 34.166333474</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
@@ -1198,17 +1198,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1215, 1216, 1217, 1218, 1223, 1224</t>
+          <t>1191, 1192, 1193, 1197, 1198, 1199</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1209.0, 1210.0, 1211.0, 1212.0, 1207.0, 1208.0</t>
+          <t>1186.0, 1187.0, 1188.0, 1183.0, 1184.0, 1185.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1R$FLavrj8G9Rxnz3lVckG, 0CIMZOOqj8GukY8gSKgU97, 18j2PWjBz3nhKzSkJrvM7d, 0wtQ7wfjD5FPd24jrI75yq, 13LOp07jD0lfjp1Ds2xiaX, 3BN76u7jD8SONfck_e054E</t>
+          <t>3Hh_lnoOjFseiPP$fBJdTk, 2P3Mbts9P06BZqiOxGDRsK, 39ETwZKMDAou$vKVot7pYG, 0WugxlnUz8xx2oGJ_ePbye, 1TuiyJHazFPP354k0XGOop, 049y1zqcb029syIWXEZkws</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>LUF:342799, LUF:342961, LUF:343164, LUF:343294, LUF:340252, LUF:342420</t>
+          <t>LUF:342961, LUF:343164, LUF:343294, LUF:340252, LUF:342420, LUF:342799</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1215, 1216, 1217, 1218, 1223, 1224</t>
+          <t>1191, 1192, 1193, 1197, 1198, 1199</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -1262,12 +1262,12 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>EG, OG1, OG2, OG3, UG2, UG1</t>
+          <t>OG1, OG2, OG3, UG2, UG1, EG</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0, 2.998, 7.939, 11.947, -8.2, -3.78</t>
+          <t>2.998, 7.94, 11.948, -8.2, -3.78, 0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr"/>
@@ -1379,22 +1379,22 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3$FY_ljDfBsweJfZwnfjOk, 0b93QOWH141xpbKCpGErNs, 0b93QOWH141xpbKCpGEr8x, 3ol_0stLL7q8pSNseENpkb, 3VbCMl1_928hbAKPG5Knnl, 1QH5Axl111J9SJj2E3W4vu</t>
+          <t>0b93QOWH141xpbKCpGErNs, 0b93QOWH141xpbKCpGEr8x, 3ol_0stLL7q8pSNseENpkb, 3VbCMl1_928hbAKPG5Knnl, 1QH5Axl111J9SJj2E3W4vu, 3$FY_ljDfBsweJfZwnfjOk</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>3.0, 4.941, 4.008, 2.523, 4.42, 3.421</t>
+          <t>4.942, 4.008, 2.522, 4.42, 3.42, 3.0</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>58.6046173021893, 7.38232192035912, 7.49144557435166, 7.38098313865425</t>
+          <t>7.38232192035912, 7.49144557435166, 7.38098313865425, 58.6046173021893</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>89.2932525, 11.4336741105, 9.274674324, 5.948525037, 10.22805901, 7.911291707</t>
+          <t>11.435988151, 9.274674324, 5.946167318, 10.22805901, 7.90897914, 89.2932525</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr"/>
@@ -1434,21 +1434,21 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>97.87437599999998</v>
+        <v>101.688451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1220, 1221, 1222</t>
+          <t>1194, 1195, 1196</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1207.0, 1208.0</t>
+          <t>1183.0, 1184.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3Q30KcAwrFjgFId43DWY8P, 34G_SBUtD7Bx_aSDXbyBOH, 11GLlly7bCgPkVa3553rnS</t>
+          <t>0flQ6A_KT1au1P6tc3jqMc, 2F6s1tVBjDqQjhbB3E6WYb, 1ob0Dr3Tb3me5ixnzVhldr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1220, 1221, 1222</t>
+          <t>1194, 1195, 1196</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1624,17 +1624,17 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>4.121, 3.421</t>
+          <t>4.12, 3.42</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>10.4407453756904, 30.404276140697, 30.8427134126076</t>
+          <t>11.5222748736684, 30.3639272858965, 30.8626322671356</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>28.0766717725, 132.984760662, 201.1249740115</t>
+          <t>42.96668072, 133.75521496, 201.07817154</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
@@ -1650,10 +1650,10 @@
       <c r="CQ4" t="inlineStr"/>
       <c r="CR4" t="inlineStr"/>
       <c r="CS4" t="n">
-        <v>39.08309449999999</v>
+        <v>42.893664</v>
       </c>
       <c r="CT4" t="n">
-        <v>58.7912815</v>
+        <v>58.794787</v>
       </c>
       <c r="CU4" t="n">
         <v>0</v>
@@ -1678,21 +1678,21 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.2703145</v>
+        <v>61.5559585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1225, 1226, 1234, 1235</t>
+          <t>1200, 1201, 1209, 1210</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1209.0, 1208.0</t>
+          <t>1185.0, 1184.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0jRMZ$SnH9ouX0ZQEwstxo, 1830E3dHD5f9qhMIKx9HB6, 14zTAK7eDFxu25AGckILdY, 3_49$ldkHAGOZei44e_8FY</t>
+          <t>3lSeJHANz4JwuuWWVWxbUH, 1s_RuZ0k90YAlXWhJ4lnX8, 3W2HgVPjj8sgJOb9kc$BUn, 3W8P9$rMX2_fA9sfb6fwqp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1225, 1226, 1234, 1235</t>
+          <t>1200, 1201, 1209, 1210</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1868,17 +1868,17 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>3.0, 3.421</t>
+          <t>3.0, 3.42</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>7.99949280466301, 8.5115559995555, 64.0177644592462, 8.2472826954821</t>
+          <t>7.99949280466301, 8.5115559995555, 63.7340745259235, 8.2472826954821</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>10.3095015, 12.423591, 172.6924374945, 14.4110052625</t>
+          <t>10.3095015, 12.423591, 170.19885987, 14.40679275</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
@@ -1897,7 +1897,7 @@
         <v>0</v>
       </c>
       <c r="CT5" t="n">
-        <v>54.69261700000001</v>
+        <v>53.978261</v>
       </c>
       <c r="CU5" t="n">
         <v>7.5776975</v>
@@ -1926,17 +1926,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2VcirkfBf6ahuppLqfjuCo</t>
+          <t>2pH4Wqvuf1bu8FEuNmVz7e</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -2182,17 +2182,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3WAjbS9Tz63fT8SRxhsEgW</t>
+          <t>2jZ_u9g6bC0gnFdRULl6Ao</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -2438,17 +2438,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3OwC$bqnH8HPMox51VeeVy</t>
+          <t>0wQhe8bif1LOoZtbl2gXny</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -2682,21 +2682,21 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>784.1024640000001</v>
+        <v>801.9748285000001</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1236, 1237, 1238, 1239, 1241, 1242, 1243, 1244, 1245, 1249, 1250, 1251</t>
+          <t>1211, 1212, 1213, 1214, 1217, 1218, 1219, 1220, 1221, 1224, 1225, 1226</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1209.0, 1212.0</t>
+          <t>1185.0, 1188.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2smUqi2i10zRE_diOVjJhu, 2VPJztHKzE5eU2jmaJhVnb, 360G1aSpvFCuurfPO7oVVK, 2gK95MKEPE$O83dwER37Qp, 0WtOOP9cn9MBUnf0AHUQfJ, 2u0jNhx4PBahQiA_Mn0fAT, 1XvgrEk2L7Sf0_v9d5iT66, 02z0dETOLCdvSjB6spGLDD, 2dWGfk8A5FP9hGnKCxZb2t, 3Dk2HhiCr35RYXuSaVOvs6, 3AGSwy4Cv9YOBE5MpdNLQt, 0E4QXUam15QfaVaTAymHn2</t>
+          <t>0HX_qt1yzF3xKWplASPhYe, 2qXFUIy2T3SBxq9lBM4xHo, 2RrGEvz4H6O8oYwW_ERzQ6, 1AENlAVbf0FPNqAceD_OOg, 0eDs_7T5r34RBessIb8ALy, 2KTKdUnXz3EAT3eZQsBIVW, 1dm6hXA1TAHxySfbOH_SuE, 3Ko5GwjxPFa8wWHDHgsYet, 0bj3cexLz16A$8LPJ5vRgB, 2CKlKmb3L8if01dRSHZkQk, 3VSDX0a6j5R9Sc3ExLWrsf, 1DAsWzcd53mxYOR7lJYiHX</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1236, 1237, 1238, 1239, 1241, 1242, 1243, 1244, 1245, 1249, 1250, 1251</t>
+          <t>1211, 1212, 1213, 1214, 1217, 1218, 1219, 1220, 1221, 1224, 1225, 1226</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0, 11.947</t>
+          <t>0.0, 11.948</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr"/>
@@ -2872,17 +2872,17 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>1.0, 1.001</t>
+          <t>1.0, 0.99800585493958, 1.00002454702819</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>93.1053783306551, 26.6148846931745, 22.6274169979695, 26.6132231953422, 18.0302029491287, 46.5550926093682, 10.2950212176134, 5.40536512706288, 51.1635370017265, 118.876854433513, 36.0606998520392, 12.0248764381316</t>
+          <t>93.1053783306551, 26.6601989972909, 25.0995479191626, 26.6595601224005, 18.0302029491287, 46.5550926093682, 10.2950212176134, 5.40536512706288, 51.1635370017265, 118.873554291617, 36.0606998520392, 12.0248764381316</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>330.8825295, 29.448249831, 32.032, 29.4479620435, 7.9934815, 136.0412375, 6.29499, 1.4047875, 17.796225, 162.444519, 25.4851555, 4.922164</t>
+          <t>330.8825295, 29.3330605, 49.998075, 29.2738285959701, 7.9934815, 136.0412375, 6.29499, 1.4047875, 17.796225, 162.494789666272, 25.4851555, 4.922164</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>693.2650895</v>
+        <v>693.3113715</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>90.8373745</v>
+        <v>108.663457</v>
       </c>
     </row>
     <row r="10">
@@ -2930,21 +2930,21 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>880.1147865</v>
+        <v>878.8663225</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1252, 1253, 1259</t>
+          <t>1227, 1228, 1235</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1212.0, 1209.0</t>
+          <t>1188.0, 1185.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2MZESDDfb379fB261rIbnR, 2VPSmwn8f80wlwsZLQwj7f, 3vBeHUwhfB5OcVQruWBfzN</t>
+          <t>2jDi0spfj5xugCuK32MU8B, 1JP2teRZzAKhVlWoAk44Gi, 0cuCI57f5FDx6c5xjTH_wt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1252, 1253, 1259</t>
+          <t>1227, 1228, 1235</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>11.947, 0.0</t>
+          <t>11.948, 0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr"/>
@@ -3120,17 +3120,17 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>1.001, 1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>61.8367587494543, 61.8374883969868, 228.018781084836</t>
+          <t>61.8686530336046, 61.8746072005705, 228.018850694891</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>126.3246569585, 126.372891645, 627.669683</t>
+          <t>125.579465, 125.616293, 627.6705645</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
@@ -3164,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="CU10" t="n">
-        <v>627.669683</v>
+        <v>627.6705645</v>
       </c>
       <c r="CV10" t="n">
         <v>0</v>
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="CX10" t="n">
-        <v>252.4451035</v>
+        <v>251.195758</v>
       </c>
     </row>
     <row r="11">
@@ -3186,21 +3186,21 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>73.566976</v>
+        <v>73.5662785</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3dUr5q39zEXBCsj4PLV405</t>
+          <t>3sBsqaQPb0euZE5Csd1V40</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -3376,17 +3376,17 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.00000564844451</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>36.5379660958738</t>
+          <t>36.5380755997099</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>73.566976</t>
+          <t>73.5666940350422</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>73.566976</v>
+        <v>73.5662785</v>
       </c>
       <c r="CV11" t="n">
         <v>0</v>
@@ -3438,21 +3438,21 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>295.86007</v>
+        <v>295.8120275</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2F9RWBhUfEZ8$cJ_kTeVpx</t>
+          <t>0owNcgsrLCORAeZymoLxMZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -3624,17 +3624,17 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.00001430884626</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>70.7275988525333</t>
+          <t>70.7243967332807</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>295.86007</t>
+          <t>295.816260228824</t>
         </is>
       </c>
       <c r="CK12" t="inlineStr">
@@ -3668,7 +3668,7 @@
         <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>295.86007</v>
+        <v>295.8120275</v>
       </c>
       <c r="CV12" t="n">
         <v>0</v>
@@ -3694,17 +3694,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>07p_i19HfFMxUYszLXHx0R</t>
+          <t>1y6$NkJCn2eRH9vQ05Vfth</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -3946,21 +3946,21 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>389.091511</v>
+        <v>389.1074575</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1230, 1231, 1232, 1233, 1240</t>
+          <t>1206, 1207, 1208, 1215, 1216</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3vSADXkCf9CehgpLlu0Bds, 2vZ$D3URf34vJnBMMHx9xX, 1D6v$lAcHDiAsIdGYCYrg4, 14Y66SGP5Fm8iYaOLsp2V8, 0XbzWrb4P70RH_r69FZvNC</t>
+          <t>367VhQ1U19B8v9mWQKmOzz, 2Hxz6DXsT92vehhFG6_ShJ, 38tAZDumv6$hnRXN0FwtYj, 2vghzoGT51TxNQvOAAv0j4, 2rIGmJBcz82eOKIU2HIoRF</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>UUF:343913, UUF:343919, UUF:344049, UUF:344052, UUF:343895</t>
+          <t>UUF:343919, UUF:344049, UUF:344052, UUF:343895, UUF:343913</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1230, 1231, 1232, 1233, 1240</t>
+          <t>1206, 1207, 1208, 1215, 1216</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -4131,22 +4131,22 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEG, 3qJ9B5zvT7$hh913fcAFEM, 3qJ9B5zvT7$hh913fcAFC8, 3qJ9B5zvT7$hh913fcAFCD, 3qJ9B5zvT7$hh913fcAFEk</t>
+          <t>3qJ9B5zvT7$hh913fcAFEM, 3qJ9B5zvT7$hh913fcAFC8, 3qJ9B5zvT7$hh913fcAFCD, 3qJ9B5zvT7$hh913fcAFEk, 3qJ9B5zvT7$hh913fcAFEG</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0, 1.00001926331646</t>
         </is>
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>28.3650362774305, 27.1971243796257, 165.175783539062, 32.1979140750708, 71.8572432719856</t>
+          <t>27.1053636632595, 164.979919618776, 32.1979140750708, 71.8572432719856, 28.8364393051884</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t>13.032036, 35.7954435, 258.794827, 56.537983, 24.9312215</t>
+          <t>35.456544, 259.062335, 56.537983, 24.9317017580095, 13.119374</t>
         </is>
       </c>
       <c r="CK14" t="inlineStr">
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>389.091511</v>
+        <v>389.1074575</v>
       </c>
       <c r="CV14" t="n">
         <v>0</v>
@@ -4198,17 +4198,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1MqvEZmU539xzlBdmFG0Gt</t>
+          <t>0a48Ih65rFx8QfDnXMMhEl</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -4450,17 +4450,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3eJReeN3j08hoB6uk90Meh</t>
+          <t>3Zzx4L78nBqBHz3ZA4ivSQ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -4702,17 +4702,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2jn0CO4WT6agpI_e3theVz</t>
+          <t>30_jhjUID1lOEnoZkbwPlR</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -4954,17 +4954,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0R6CzIVUf9Xg$xY9ZGMPOI</t>
+          <t>3v_If9$uz3fwzdtVKMHQ8o</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -5202,17 +5202,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1211.0</t>
+          <t>1187.0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0mgHCA5Bj2q8PGPshAJwdu</t>
+          <t>2EdAa2vnvDwv$K313aI9nH</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>7.939</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr"/>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="CH19" t="inlineStr">
         <is>
-          <t>3.579</t>
+          <t>3.578</t>
         </is>
       </c>
       <c r="CI19" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="CJ19" t="inlineStr">
         <is>
-          <t>62.8941696375</t>
+          <t>62.876596525</t>
         </is>
       </c>
       <c r="CK19" t="inlineStr">
@@ -5450,17 +5450,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2q$FhMpurDpQLxyHcG7QMH</t>
+          <t>0snplPWT179OZgXqJkFdam</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -5702,17 +5702,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0lrhQ1hBL3UB9wu$bziAIW</t>
+          <t>1PFX2sV$1EtwB4cgbdYiiR</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -5950,17 +5950,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>15q5B8t2H1jOLW$YLJTSCd</t>
+          <t>3QuKuIVNvEDebBjhENRHdp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -6202,17 +6202,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1PXOCrKLD2ohK81bqcw5L8</t>
+          <t>1nHVq1BLj3N83VoxI$QAiV</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -6450,17 +6450,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>37pvr1fmPFoPR8VqDaFSaH</t>
+          <t>1xAkayK$92b8rEYvsI7ddA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -6702,21 +6702,21 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>123.877062</v>
+        <v>123.8381265</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0x9I5spTf0W8z7GhPCk1ky</t>
+          <t>3tE0xz5ivFbule77FUWYT7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -6893,12 +6893,12 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>70.773328385831</t>
+          <t>70.7806751860665</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
         <is>
-          <t>371.631186</t>
+          <t>371.5143795</t>
         </is>
       </c>
       <c r="CK25" t="inlineStr">
@@ -6928,7 +6928,7 @@
         <v>0</v>
       </c>
       <c r="CU25" t="n">
-        <v>123.877062</v>
+        <v>123.8381265</v>
       </c>
       <c r="CV25" t="n">
         <v>0</v>
@@ -6954,17 +6954,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1208.0</t>
+          <t>1184.0</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2VOStX3MjEzAywBgrc2Ymz</t>
+          <t>2b761ZbMf7OQyYTjBYwlqS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="CH26" t="inlineStr">
         <is>
-          <t>3.421</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CI26" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="CJ26" t="inlineStr">
         <is>
-          <t>9.9019596335</t>
+          <t>9.89906517</t>
         </is>
       </c>
       <c r="CK26" t="inlineStr">
@@ -7206,17 +7206,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1208.0</t>
+          <t>1184.0</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1K1FlaQx1EExBCUKfCbQFS</t>
+          <t>2TkX3v9lLDHfNhAwV_173q</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="CH27" t="inlineStr">
         <is>
-          <t>3.421</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CI27" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="CJ27" t="inlineStr">
         <is>
-          <t>9.302537145</t>
+          <t>9.2998179</t>
         </is>
       </c>
       <c r="CK27" t="inlineStr">
@@ -7458,17 +7458,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1208.0</t>
+          <t>1184.0</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1R9Imo_5167B$XHbYy7aZ6</t>
+          <t>0bebBo2BjBix6YQ7lpTjg5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="CH28" t="inlineStr">
         <is>
-          <t>3.421</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CI28" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CJ28" t="inlineStr">
         <is>
-          <t>86.486010215</t>
+          <t>86.4607293</t>
         </is>
       </c>
       <c r="CK28" t="inlineStr">
@@ -7714,17 +7714,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1265, 1266</t>
+          <t>1241, 1242</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1207.0, 1208.0</t>
+          <t>1183.0, 1184.0</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2v3d7GGqDEd8IyrTdRXWWY, 2_kl8xFAvE_Oi0Djmy1jeA</t>
+          <t>3P24pHOeX7huTaoUa46vgT, 0OAGNaNgv3wwzf3ckQ_KTm</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1265, 1266</t>
+          <t>1241, 1242</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="CH29" t="inlineStr">
         <is>
-          <t>4.121, 3.421</t>
+          <t>4.11999999999999, 3.42</t>
         </is>
       </c>
       <c r="CI29" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="CJ29" t="inlineStr">
         <is>
-          <t>280.5307801725, 47.176842086</t>
+          <t>280.462706699999, 47.16305172</t>
         </is>
       </c>
       <c r="CK29" t="inlineStr">
@@ -7970,17 +7970,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1207.0</t>
+          <t>1183.0</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3LuW9jHbHBBAyJit_$Yn3$</t>
+          <t>3EFA13Ox1F58pYx6_i5NyU</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="CH30" t="inlineStr">
         <is>
-          <t>4.121</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="CI30" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CJ30" t="inlineStr">
         <is>
-          <t>537.6245535115</t>
+          <t>537.49409378</t>
         </is>
       </c>
       <c r="CK30" t="inlineStr">
@@ -8226,17 +8226,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1207.0</t>
+          <t>1183.0</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0ZrdVUR4b0zxBrw6VrPmpy</t>
+          <t>0VzQ2RIZnBkuyXmMpvbN9_</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="CH31" t="inlineStr">
         <is>
-          <t>4.121</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="CI31" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="CJ31" t="inlineStr">
         <is>
-          <t>160.148014845</t>
+          <t>160.1091534</t>
         </is>
       </c>
       <c r="CK31" t="inlineStr">
@@ -8478,21 +8478,21 @@
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>3885.43503</v>
+        <v>3885.5616805</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1309, 1311, 1317, 1324, 1329, 1333</t>
+          <t>1285, 1287, 1293, 1300, 1305, 1309</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1207.0, 1208.0, 1209.0, 1210.0, 1211.0, 1212.0</t>
+          <t>1183.0, 1184.0, 1185.0, 1186.0, 1187.0, 1188.0</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>220mi7GG59YuA9V0nhWv8f, 1CV6oaRyn1HQP8tN4myNln, 2JYUQcEU93zwiGeMtni83Z, 2O9cNxLZXB48ei75HpXuVM, 2E_TZJZ7r4DgKH0p0YQJl8, 1AmWYBKrzAYQ$BPe2iH8In</t>
+          <t>11rtg$OHHCQgjPenPfbWHc, 1IKxMLTg96xBLZwOLJkOep, 2lJbeNWPr69PR6Bv8eHLx5, 0sM00mZHr6DOEYTFqh$IrG, 0rjMKvNtzAnefNaYJ97j52, 0qFk07a55D6POPpcM5bCmf</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1309, 1311, 1317, 1324, 1329, 1333</t>
+          <t>1285, 1287, 1293, 1300, 1305, 1309</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>-8.2, -3.78, 0.0, 2.998, 7.939, 11.947</t>
+          <t>-8.2, -3.78, 0.0, 2.998, 7.94, 11.948</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr"/>
@@ -8633,12 +8633,12 @@
       </c>
       <c r="CI32" t="inlineStr">
         <is>
-          <t>123.779783200545, 126.058990957543, 108.708999464787, 104.920885573921, 104.909626929904, 50.8161667005644</t>
+          <t>123.77898440477, 126.05717405587, 108.706025323265, 104.920885573921, 104.909626929904, 50.8161667005644</t>
         </is>
       </c>
       <c r="CJ32" t="inlineStr">
         <is>
-          <t>946.7568455, 944.3010395, 635.4141235, 607.3553475, 607.3728175, 144.2348565</t>
+          <t>946.7966155, 944.3288025, 635.473241, 607.3553475, 607.3728175, 144.2348565</t>
         </is>
       </c>
       <c r="CK32" t="inlineStr"/>
@@ -8650,13 +8650,13 @@
       <c r="CQ32" t="inlineStr"/>
       <c r="CR32" t="inlineStr"/>
       <c r="CS32" t="n">
-        <v>946.7568455000001</v>
+        <v>946.7966155</v>
       </c>
       <c r="CT32" t="n">
-        <v>944.3010395</v>
+        <v>944.3288025000001</v>
       </c>
       <c r="CU32" t="n">
-        <v>635.4141235</v>
+        <v>635.473241</v>
       </c>
       <c r="CV32" t="n">
         <v>607.3553475</v>
@@ -8678,21 +8678,21 @@
         <v>11</v>
       </c>
       <c r="C33" t="n">
-        <v>5484.661963</v>
+        <v>5484.879056999999</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1307, 1308, 1310, 1314, 1315, 1316, 1321, 1322, 1323, 1328, 1332</t>
+          <t>1283, 1284, 1286, 1290, 1291, 1292, 1297, 1298, 1299, 1304, 1308</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1207.0, 1208.0, 1209.0, 1210.0, 1211.0, 1212.0</t>
+          <t>1183.0, 1184.0, 1185.0, 1186.0, 1187.0, 1188.0</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2h61zMFo5AJAPRusVng_Xn, 1ocReKPMH6yQHek4DHBHWe, 1WVo1W$JrFBwJk1Ud33P2_, 2tu7qWjqT2KwS8C7vq8SbN, 2rXFWc8jX9X9uAiF4mg4_c, 1xVbGem8z8Yw7KMlDD7tyl, 29mRuo3Gj2kAoruOaOpQPk, 2UYbzXfWX4jeekEZZounLu, 2iqV3awXnFaPEu0T7HAtp4, 2HDdALzov8sOiati08LIYR, 191C_eUqLBjwUYQYjuyzbJ</t>
+          <t>2g7lHgM9fCfeWFLbqCROTN, 2TjpIVE3fEjf2yeWwF5tbt, 37U7QqRiD3K8YpI0EDvqEG, 3Phqv9RFv0aPLT5D_Im9QT, 2CTrriW1D4XfbevcRhL0D$, 3ue0$unPz0uux7AwL1STF3, 0BPV577Cv2qOXbm$_0BLlX, 0D49X8G8b21vMvV9fI6DYy, 3QbhoocVL16heqVtso3nIe, 1vS9xL68j7QRd7X5GTAvLE, 1MeUygKbr5gwqhdLnI1$fr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1307, 1308, 1310, 1314, 1315, 1316, 1321, 1322, 1323, 1328, 1332</t>
+          <t>1283, 1284, 1286, 1290, 1291, 1292, 1297, 1298, 1299, 1304, 1308</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>-8.2, -3.78, 0.0, 2.998, 7.939, 11.947</t>
+          <t>-8.2, -3.78, 0.0, 2.998, 7.94, 11.948</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr"/>
@@ -8828,17 +8828,17 @@
       <c r="CG33" t="inlineStr"/>
       <c r="CH33" t="inlineStr">
         <is>
-          <t>4.42, 0.5, 3.78, 2.998, 0.66, 4.281, 4.009, 2.522</t>
+          <t>4.42, 0.5, 3.78, 2.998, 0.66, 4.282, 4.008, 2.522</t>
         </is>
       </c>
       <c r="CI33" t="inlineStr">
         <is>
-          <t>123.779783200545, 96.2201716288239, 126.058990957543, 110.604319237956, 108.708999464787, 64.449354629798, 104.920885573921, 4.39171104230114, 30.6419719936692, 104.909626929904, 50.8161667005644</t>
+          <t>123.77898440477, 96.1953347530367, 126.05717405587, 110.601345096434, 108.706025323265, 64.449354629798, 104.920885573921, 4.39171104230114, 30.6419719936692, 104.909626929904, 50.8161667005644</t>
         </is>
       </c>
       <c r="CJ33" t="inlineStr">
         <is>
-          <t>4184.66525711, 473.3741925, 3569.45792931, 1897.89404823, 419.37332151, 5.79328175, 2600.0882426475, 1.18212025, 2.7371795, 2434.9576253575, 363.760308093</t>
+          <t>4184.84104051, 473.3898555, 3569.56287345, 1898.071282495, 419.41233906, 5.79328175, 2600.695597995, 1.18212025, 2.7371795, 2434.35025254, 363.760308093</t>
         </is>
       </c>
       <c r="CK33" t="inlineStr"/>
@@ -8850,13 +8850,13 @@
       <c r="CQ33" t="inlineStr"/>
       <c r="CR33" t="inlineStr"/>
       <c r="CS33" t="n">
-        <v>1893.5052305</v>
+        <v>1893.5763265</v>
       </c>
       <c r="CT33" t="n">
-        <v>944.3010395</v>
+        <v>944.3288025000001</v>
       </c>
       <c r="CU33" t="n">
-        <v>1280.054072</v>
+        <v>1280.172307</v>
       </c>
       <c r="CV33" t="n">
         <v>615.1939470000001</v>
@@ -8882,17 +8882,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2rnYpcA2j5ORd2uupGEvG0</t>
+          <t>1elxkk8h12l8VI66SES48s</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -9134,17 +9134,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1207.0</t>
+          <t>1183.0</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>21ftMaN2H3x9V_1Iuv7_Lz</t>
+          <t>2jQqxIN7D0G9XrN3psKCHB</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="CH35" t="inlineStr">
         <is>
-          <t>4.121</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="CI35" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="CJ35" t="inlineStr">
         <is>
-          <t>47.4119380995</t>
+          <t>47.40043314</t>
         </is>
       </c>
       <c r="CK35" t="inlineStr">
@@ -9382,21 +9382,21 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>24.194584</v>
+        <v>24.251362</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1207.0</t>
+          <t>1183.0</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0kB0A2S5z5auQg3$i3qAjO</t>
+          <t>0SfLsfaY1DQQexHNkqpPq8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -9572,17 +9572,17 @@
       </c>
       <c r="CH36" t="inlineStr">
         <is>
-          <t>4.121</t>
+          <t>4.12000209952917</t>
         </is>
       </c>
       <c r="CI36" t="inlineStr">
         <is>
-          <t>25.4703597146799</t>
+          <t>25.4721434358016</t>
         </is>
       </c>
       <c r="CJ36" t="inlineStr">
         <is>
-          <t>99.705880664</t>
+          <t>99.9156623564419</t>
         </is>
       </c>
       <c r="CK36" t="inlineStr">
@@ -9606,7 +9606,7 @@
       <c r="CQ36" t="inlineStr"/>
       <c r="CR36" t="inlineStr"/>
       <c r="CS36" t="n">
-        <v>24.194584</v>
+        <v>24.251362</v>
       </c>
       <c r="CT36" t="n">
         <v>0</v>
@@ -9634,21 +9634,21 @@
         <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>7.9612265</v>
+        <v>8.0182985</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1283, 1284</t>
+          <t>1259, 1260</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1208.0, 1211.0</t>
+          <t>1184.0, 1187.0</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3fS1w73ELCBRUIqHWvP3$z, 2FQ8B6_JP08wqgDmUUSwZn</t>
+          <t>25qvKAslv4su4AGnfPnQAy, 0$R0qHln98kepMxkmwzDXO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1283, 1284</t>
+          <t>1259, 1260</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -9707,7 +9707,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>-3.78, 7.939</t>
+          <t>-3.78, 7.94</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr"/>
@@ -9824,17 +9824,17 @@
       </c>
       <c r="CH37" t="inlineStr">
         <is>
-          <t>3.421, 3.579</t>
+          <t>3.42000189301365, 3.578</t>
         </is>
       </c>
       <c r="CI37" t="inlineStr">
         <is>
-          <t>9.48071596737105, 8.46504079502658</t>
+          <t>9.60078202998561, 8.46504079502658</t>
         </is>
       </c>
       <c r="CJ37" t="inlineStr">
         <is>
-          <t>12.255739342, 15.6714549855</t>
+          <t>12.4473499697633, 15.667076261</t>
         </is>
       </c>
       <c r="CK37" t="inlineStr">
@@ -9861,7 +9861,7 @@
         <v>0</v>
       </c>
       <c r="CT37" t="n">
-        <v>3.582502</v>
+        <v>3.639574</v>
       </c>
       <c r="CU37" t="n">
         <v>0</v>
@@ -9890,17 +9890,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0qoMVDV8fAzBp8ww__y4Tz</t>
+          <t>1KAZImcajE19VMZ2urkS9A</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -10138,21 +10138,21 @@
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>34.123994</v>
+        <v>34.1596555</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0teRCO0lj5OQYpPkvQztRq</t>
+          <t>0p4XPibzXDmfYuHdDNQKoi</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -10329,12 +10329,12 @@
       </c>
       <c r="CI39" t="inlineStr">
         <is>
-          <t>32.1201520903664</t>
+          <t>32.1152224910364</t>
         </is>
       </c>
       <c r="CJ39" t="inlineStr">
         <is>
-          <t>34.123994</t>
+          <t>34.1596555</t>
         </is>
       </c>
       <c r="CK39" t="inlineStr">
@@ -10364,7 +10364,7 @@
         <v>0</v>
       </c>
       <c r="CU39" t="n">
-        <v>34.123994</v>
+        <v>34.1596555</v>
       </c>
       <c r="CV39" t="n">
         <v>0</v>
@@ -10390,17 +10390,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1269, 1270</t>
+          <t>1245, 1246</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1208.0</t>
+          <t>1184.0</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1F3Fkq$vj7GQErmS_ow7lc, 1acftYr2jDufGYUUZLoAmB</t>
+          <t>2DRzef4hn3IgIiLgkhkHE9, 2EaietiEbAIPhvSO2Cvy$b</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1269, 1270</t>
+          <t>1245, 1246</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CH40" t="inlineStr">
         <is>
-          <t>3.421</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CI40" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="CJ40" t="inlineStr">
         <is>
-          <t>53.202950691, 54.077371975</t>
+          <t>53.18739882, 54.0615645</t>
         </is>
       </c>
       <c r="CK40" t="inlineStr">
@@ -10638,21 +10638,21 @@
         <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>168.6224655</v>
+        <v>169.608867</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1271, 1272, 1275, 1276</t>
+          <t>1247, 1248, 1250, 1251</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1208.0</t>
+          <t>1184.0</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1vDbowLhr7nx5SdmnF8FXc, 2oV52czXD7zAOL8XOUSL78, 1d_UGp1UD2pfCq6QCu1odj, 1DjBk084n8gfRcElXcnhlR</t>
+          <t>2_ozTiGP19wxfIiizV$YDP, 1hrw6SBSX5_xz0kjcf$lQq, 3MbScePwXCG951Z0r4L0yN, 3YWB1QD45A0ffgE_grSlSK</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1271, 1272, 1275, 1276</t>
+          <t>1247, 1248, 1250, 1251</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -10828,17 +10828,17 @@
       </c>
       <c r="CH41" t="inlineStr">
         <is>
-          <t>3.421</t>
+          <t>3.42, 3.4200048337541, 3.4200029159233</t>
         </is>
       </c>
       <c r="CI41" t="inlineStr">
         <is>
-          <t>38.5924363426088, 38.5665051072028, 38.597841235775, 38.5011315279237</t>
+          <t>38.4721477169385, 38.4494075508202, 38.4766189708997, 38.3845491226873</t>
         </is>
       </c>
       <c r="CJ41" t="inlineStr">
         <is>
-          <t>144.861656588, 143.9881367375, 144.686432968, 143.321228182</t>
+          <t>145.67164074, 144.77602082301, 145.500128674635, 144.11486358</t>
         </is>
       </c>
       <c r="CK41" t="inlineStr">
@@ -10865,7 +10865,7 @@
         <v>0</v>
       </c>
       <c r="CT41" t="n">
-        <v>168.6224655</v>
+        <v>169.608867</v>
       </c>
       <c r="CU41" t="n">
         <v>0</v>
@@ -10890,21 +10890,21 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>13.396027</v>
+        <v>13.502395</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>3O5OUxbKP5_PZAUUrtfSgZ</t>
+          <t>3vzyyhvhTCCxHI3Ujz_Pdk</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -11085,12 +11085,12 @@
       </c>
       <c r="CI42" t="inlineStr">
         <is>
-          <t>13.0853052853127</t>
+          <t>13.1107742818786</t>
         </is>
       </c>
       <c r="CJ42" t="inlineStr">
         <is>
-          <t>40.188081</t>
+          <t>40.507185</t>
         </is>
       </c>
       <c r="CK42" t="inlineStr">
@@ -11120,7 +11120,7 @@
         <v>0</v>
       </c>
       <c r="CU42" t="n">
-        <v>13.396027</v>
+        <v>13.502395</v>
       </c>
       <c r="CV42" t="n">
         <v>0</v>
@@ -11146,17 +11146,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1210.0</t>
+          <t>1186.0</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1MPw1r9hv6$h6AZYdCPJK4</t>
+          <t>2lK1NiaZXE9g_b2KyM_qzf</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -11398,17 +11398,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1273, 1278</t>
+          <t>1252, 1253</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1210.0, 1207.0</t>
+          <t>1183.0, 1186.0</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1FDFHpwUH4NB1tapjSpmKb, 1OOeb7pNP5YhVqjcacSVQj</t>
+          <t>0fphzOn3z3ffzYnIZDfkRZ, 3$MWY95kL37xnSaojxj3cW</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -11428,12 +11428,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SGR:342955, SGR:340482</t>
+          <t>SGR:340482, SGR:342955</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1273, 1278</t>
+          <t>1252, 1253</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -11462,12 +11462,12 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>OG1, UG2</t>
+          <t>UG2, OG1</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>2.998, -8.2</t>
+          <t>-8.2, 2.998</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr"/>
@@ -11579,22 +11579,22 @@
       </c>
       <c r="CG44" t="inlineStr">
         <is>
-          <t>0b93QOWH141xpbKCpGErNi, 3VbCMl1_928hbAKPG5Knzn</t>
+          <t>3VbCMl1_928hbAKPG5Knzn, 0b93QOWH141xpbKCpGErNi</t>
         </is>
       </c>
       <c r="CH44" t="inlineStr">
         <is>
-          <t>3.982, 4.121</t>
+          <t>4.12, 3.982</t>
         </is>
       </c>
       <c r="CI44" t="inlineStr">
         <is>
-          <t>41.7997852969898, 37.9925325891083</t>
+          <t>37.9925325891083, 41.7997852969898</t>
         </is>
       </c>
       <c r="CJ44" t="inlineStr">
         <is>
-          <t>356.711573856, 370.300717605</t>
+          <t>370.2108606, 356.711573856</t>
         </is>
       </c>
       <c r="CK44" t="inlineStr">
@@ -11650,17 +11650,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1277, 1282</t>
+          <t>1257, 1258</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1210.0, 1207.0</t>
+          <t>1183.0, 1186.0</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2qwEpCHpPBQhWqR0aH8a_c, 3fqw08GKT8VB$WT6lvspWB</t>
+          <t>1mK10My2H1Jf6TH2FFyNJl, 0v8vKsFUHEhuGCI94TqyuL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -11680,12 +11680,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>SPH:342964, SPH:340222</t>
+          <t>SPH:340222, SPH:342964</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1277, 1282</t>
+          <t>1257, 1258</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -11714,12 +11714,12 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>OG1, UG2</t>
+          <t>UG2, OG1</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>2.998, -8.2</t>
+          <t>-8.2, 2.998</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr"/>
@@ -11831,22 +11831,22 @@
       </c>
       <c r="CG45" t="inlineStr">
         <is>
-          <t>0b93QOWH141xpbKCpGErNp, 27eKs3mJf3tucFrDswOcPu</t>
+          <t>27eKs3mJf3tucFrDswOcPu, 0b93QOWH141xpbKCpGErNp</t>
         </is>
       </c>
       <c r="CH45" t="inlineStr">
         <is>
-          <t>7.85999999999999, 8.2</t>
+          <t>8.2, 7.85999999999999</t>
         </is>
       </c>
       <c r="CI45" t="inlineStr">
         <is>
-          <t>89.0985551917371, 89.0980990398666</t>
+          <t>89.0980990398666, 89.0985551917371</t>
         </is>
       </c>
       <c r="CJ45" t="inlineStr">
         <is>
-          <t>3642.20571486, 3799.6835198</t>
+          <t>3799.6835198, 3642.20571486</t>
         </is>
       </c>
       <c r="CK45" t="inlineStr">
@@ -11918,17 +11918,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1301, 1302</t>
+          <t>1277, 1278</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1208.0, 1211.0</t>
+          <t>1184.0, 1187.0</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2goFLwB6DCTwDTgbAWEEIH, 0d65XwDRr8KPZICzeqHSW5</t>
+          <t>2gsiWFr2TB1AHTbv7ojX6m, 3jgApaggT6VOj2drGLqhV$</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1301, 1302</t>
+          <t>1277, 1278</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>-3.78, 7.939</t>
+          <t>-3.78, 7.94</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr"/>
@@ -12104,7 +12104,7 @@
       </c>
       <c r="CH46" t="inlineStr">
         <is>
-          <t>3.421, 3.579</t>
+          <t>3.42, 3.578</t>
         </is>
       </c>
       <c r="CI46" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="CJ46" t="inlineStr">
         <is>
-          <t>31.631373356, 22.839338394</t>
+          <t>31.62212712, 22.832956908</t>
         </is>
       </c>
       <c r="CK46" t="inlineStr">
@@ -12170,17 +12170,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1303, 1304</t>
+          <t>1279, 1280</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1208.0, 1211.0</t>
+          <t>1184.0, 1187.0</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0WJ65NDaH54RWZcOZo2hFz, 0DQARhKmnCX83BGrsfeEgq</t>
+          <t>0L$CPopvL2ng78uaCkxmd2, 2R0Ko1_rT45gQWRWnSw8Rh</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1303, 1304</t>
+          <t>1279, 1280</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -12239,7 +12239,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>-3.78, 7.939</t>
+          <t>-3.78, 7.94</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr"/>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="CH47" t="inlineStr">
         <is>
-          <t>3.421, 3.579</t>
+          <t>3.42, 3.578</t>
         </is>
       </c>
       <c r="CI47" t="inlineStr">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="CJ47" t="inlineStr">
         <is>
-          <t>37.7632815175, 16.325379444</t>
+          <t>37.75224285, 16.320818008</t>
         </is>
       </c>
       <c r="CK47" t="inlineStr">
@@ -12422,17 +12422,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1208.0</t>
+          <t>1184.0</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1wnl70Hcf4J91aH6kWoQ5w</t>
+          <t>2pxOd96v91mxlwof2bdwwu</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="CH48" t="inlineStr">
         <is>
-          <t>3.421</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CI48" t="inlineStr">
@@ -12618,7 +12618,7 @@
       </c>
       <c r="CJ48" t="inlineStr">
         <is>
-          <t>13.460331599</t>
+          <t>13.45639698</t>
         </is>
       </c>
       <c r="CK48" t="inlineStr">
@@ -12674,17 +12674,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1212.0</t>
+          <t>1188.0</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>3542EqJCz3j9Eu7i7LwKQI</t>
+          <t>2RQb_YuIX0cupTG8njrqa5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -12709,7 +12709,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -12743,7 +12743,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>11.947</t>
+          <t>11.948</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr"/>
@@ -12922,17 +12922,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1H1NJxt1P4dhBGOFdbv$N4</t>
+          <t>3V04x_Gn9CsOd3mf5kjSS7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -13174,17 +13174,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1212.0</t>
+          <t>1188.0</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1xCUaRipzEBRjcRGOUa__w</t>
+          <t>0ydbChVXH5YeiOECwP0lP5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -13209,7 +13209,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -13243,7 +13243,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>11.947</t>
+          <t>11.948</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr"/>
@@ -13426,17 +13426,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1212.0</t>
+          <t>1188.0</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>3gQV9bpHv7NfVbjzlui7Lj</t>
+          <t>3865N6dr5D2QZmKnsV5UjA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>11.947</t>
+          <t>11.948</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr"/>
@@ -13674,17 +13674,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1212.0</t>
+          <t>1188.0</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0x5OAt7GXB6Rq0gRG_tICL</t>
+          <t>2dCF9Z2NrCiPs79T_2XETx</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -13743,7 +13743,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>11.947</t>
+          <t>11.948</t>
         </is>
       </c>
       <c r="AH53" t="inlineStr"/>
@@ -13922,17 +13922,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1209.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1nbtU4bcH2MeFbv04K7ZN2</t>
+          <t>3th3YBjLPEbgeAFO8BnVLM</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -13957,7 +13957,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -14178,17 +14178,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1211.0</t>
+          <t>1187.0</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0CmilJIZr6B8RyG4QW7HcZ</t>
+          <t>2V_TDJQGX5u9IXI55MWQFM</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -14247,7 +14247,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>7.939</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="AH55" t="inlineStr"/>
@@ -14360,7 +14360,7 @@
       </c>
       <c r="CH55" t="inlineStr">
         <is>
-          <t>3.579</t>
+          <t>3.578</t>
         </is>
       </c>
       <c r="CI55" t="inlineStr">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="CJ55" t="inlineStr">
         <is>
-          <t>185.281043418</t>
+          <t>185.229274476</t>
         </is>
       </c>
       <c r="CK55" t="inlineStr">
@@ -14422,21 +14422,21 @@
         <v>6</v>
       </c>
       <c r="C56" t="n">
-        <v>164.6158945</v>
+        <v>166.5463805</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1313, 1319, 1320, 1325, 1326, 1331</t>
+          <t>1289, 1295, 1296, 1301, 1302, 1307</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1209.0, 1210.0, 1211.0, 1212.0</t>
+          <t>1185.0, 1186.0, 1187.0, 1188.0</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1dO_bQkdz9nwDyTkTE7ib2, 1Bex$LLBz14RGCBVd_3SHQ, 0s4lbBN6v2wQ56baFu8aCK, 19fOi9h4H1XBR85Agg_fkE, 1YjQd29ADBdhHAaWT8IdQR, 2yWWAdHcT0Ee9Cxo9n9g3E</t>
+          <t>0XnoVHZ5b7YeZWNQ2bXPFm, 3aH$lMb654_u$4SW_WvFAN, 14l9pM3sL8xfYz1mvXCNWG, 0hYc3lmMH2T91sw96db3JM, 0pnXM2gsT77R5nDFj8mzSx, 3hhMFg80L1LfBHM_a3hr7A</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1313, 1319, 1320, 1325, 1326, 1331</t>
+          <t>1289, 1295, 1296, 1301, 1302, 1307</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -14495,7 +14495,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>0.0, 2.998, 7.939, 11.947</t>
+          <t>0.0, 2.998, 7.94, 11.948</t>
         </is>
       </c>
       <c r="AH56" t="inlineStr"/>
@@ -14580,17 +14580,17 @@
       </c>
       <c r="CH56" t="inlineStr">
         <is>
-          <t>1.0, 1.158, 1.001</t>
+          <t>1.0, 0.999999999999999, 0.999999999999998</t>
         </is>
       </c>
       <c r="CI56" t="inlineStr">
         <is>
-          <t>22.0715375602572, 27.2953812739153, 27.3237702962066, 28.2538110740109, 28.2852454986017, 29.8805721692127</t>
+          <t>22.1434378257397, 27.4536844116549, 27.6473031566045, 28.3136803768729, 28.4471992015421, 29.8929803703454</t>
         </is>
       </c>
       <c r="CJ56" t="inlineStr">
         <is>
-          <t>16.361301, 29.16354678, 29.354732001, 28.4928473830001, 28.6564923645001, 40.6690549264999</t>
+          <t>17.082447, 25.384223, 25.882478, 28.4057145000001, 29.2135305000001, 40.5779874999999</t>
         </is>
       </c>
       <c r="CK56" t="inlineStr"/>
@@ -14608,16 +14608,16 @@
         <v>0</v>
       </c>
       <c r="CU56" t="n">
-        <v>16.361301</v>
+        <v>17.082447</v>
       </c>
       <c r="CV56" t="n">
-        <v>50.5339195</v>
+        <v>51.266701</v>
       </c>
       <c r="CW56" t="n">
-        <v>57.0922475</v>
+        <v>57.619245</v>
       </c>
       <c r="CX56" t="n">
-        <v>40.6284265</v>
+        <v>40.5779875</v>
       </c>
     </row>
     <row r="57">
@@ -14630,21 +14630,21 @@
         <v>4</v>
       </c>
       <c r="C57" t="n">
-        <v>27.30605</v>
+        <v>41.80292</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1312, 1318, 1327, 1330</t>
+          <t>1288, 1294, 1303, 1306</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1209.0, 1210.0, 1211.0, 1212.0</t>
+          <t>1185.0, 1186.0, 1187.0, 1188.0</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>3S19U$d1v2EAwMe1MFmPkg, 0cZezKqu94ovlQgVTxGUP9, 0Dg5sNnYTBWwyKrJUXkFTO, 3eXcdEMUX3XuwJXhU1bBiW</t>
+          <t>1CcwMqeXT8UesKx8nLd6OD, 1MQDEFDcX439MvQ3uigCM$, 2$k1ahqBDFJPjWMBdR8WtC, 3r8c5tGbPC_fDRkxzKA81G</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -14669,7 +14669,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1312, 1318, 1327, 1330</t>
+          <t>1288, 1294, 1303, 1306</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -14703,7 +14703,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>0.0, 2.998, 7.939, 11.947</t>
+          <t>0.0, 2.998, 7.94, 11.948</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr"/>
@@ -14788,17 +14788,17 @@
       </c>
       <c r="CH57" t="inlineStr">
         <is>
-          <t>1.0, 1.158, 1.001</t>
+          <t>1.0, 0.999999999999999</t>
         </is>
       </c>
       <c r="CI57" t="inlineStr">
         <is>
-          <t>10.4510384173057</t>
+          <t>11.5343811888718</t>
         </is>
       </c>
       <c r="CJ57" t="inlineStr">
         <is>
-          <t>6.8265125, 7.90510147499999, 6.83333901250001, 6.8333390125</t>
+          <t>10.45073</t>
         </is>
       </c>
       <c r="CK57" t="inlineStr"/>
@@ -14816,16 +14816,16 @@
         <v>0</v>
       </c>
       <c r="CU57" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="CV57" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="CW57" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="CX57" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
     </row>
   </sheetData>
